--- a/app/_templates/wage-ledger-template.xlsx
+++ b/app/_templates/wage-ledger-template.xlsx
@@ -109,7 +109,7 @@
     <t>基本給</t>
   </si>
   <si>
-    <t>特　別　手　当</t>
+    <t>特別手当</t>
   </si>
   <si>
     <t>夜勤</t>
@@ -219,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -417,6 +417,13 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin"/>
+      <right/>
+      <top style="double"/>
+      <bottom style="dashed"/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="double"/>
@@ -431,13 +438,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right/>
-      <top style="double"/>
-      <bottom style="dashed"/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium"/>
       <top style="double"/>
@@ -466,20 +466,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="dashed"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="dashed"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin"/>
       <right/>
       <top style="dashed"/>
@@ -588,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -660,7 +646,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
@@ -696,123 +682,108 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1909,1090 +1880,1090 @@
       <c r="BQ13" s="35"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37" t="s">
+      <c r="A14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="40"/>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="40"/>
-      <c r="AA14" s="40"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="40"/>
-      <c r="AE14" s="40"/>
-      <c r="AF14" s="40"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="40"/>
-      <c r="AI14" s="40"/>
-      <c r="AJ14" s="40"/>
-      <c r="AK14" s="39"/>
-      <c r="AL14" s="40"/>
-      <c r="AM14" s="40"/>
-      <c r="AN14" s="40"/>
-      <c r="AO14" s="39"/>
-      <c r="AP14" s="40"/>
-      <c r="AQ14" s="40"/>
-      <c r="AR14" s="40"/>
-      <c r="AS14" s="39"/>
-      <c r="AT14" s="40"/>
-      <c r="AU14" s="40"/>
-      <c r="AV14" s="40"/>
-      <c r="AW14" s="39"/>
-      <c r="AX14" s="40"/>
-      <c r="AY14" s="40"/>
-      <c r="AZ14" s="40"/>
-      <c r="BA14" s="40"/>
-      <c r="BB14" s="39"/>
-      <c r="BC14" s="40"/>
-      <c r="BD14" s="40"/>
-      <c r="BE14" s="40"/>
-      <c r="BF14" s="39"/>
-      <c r="BG14" s="40"/>
-      <c r="BH14" s="40"/>
-      <c r="BI14" s="41"/>
-      <c r="BJ14" s="39"/>
-      <c r="BK14" s="40"/>
-      <c r="BL14" s="40"/>
-      <c r="BM14" s="41"/>
-      <c r="BN14" s="39">
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="37"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="37"/>
+      <c r="AD14" s="38"/>
+      <c r="AE14" s="38"/>
+      <c r="AF14" s="38"/>
+      <c r="AG14" s="37"/>
+      <c r="AH14" s="38"/>
+      <c r="AI14" s="38"/>
+      <c r="AJ14" s="38"/>
+      <c r="AK14" s="37"/>
+      <c r="AL14" s="38"/>
+      <c r="AM14" s="38"/>
+      <c r="AN14" s="38"/>
+      <c r="AO14" s="37"/>
+      <c r="AP14" s="38"/>
+      <c r="AQ14" s="38"/>
+      <c r="AR14" s="38"/>
+      <c r="AS14" s="37"/>
+      <c r="AT14" s="38"/>
+      <c r="AU14" s="38"/>
+      <c r="AV14" s="38"/>
+      <c r="AW14" s="37"/>
+      <c r="AX14" s="38"/>
+      <c r="AY14" s="38"/>
+      <c r="AZ14" s="38"/>
+      <c r="BA14" s="38"/>
+      <c r="BB14" s="37"/>
+      <c r="BC14" s="38"/>
+      <c r="BD14" s="38"/>
+      <c r="BE14" s="38"/>
+      <c r="BF14" s="37"/>
+      <c r="BG14" s="38"/>
+      <c r="BH14" s="38"/>
+      <c r="BI14" s="39"/>
+      <c r="BJ14" s="37"/>
+      <c r="BK14" s="38"/>
+      <c r="BL14" s="38"/>
+      <c r="BM14" s="39"/>
+      <c r="BN14" s="37">
         <f>SUM(I14:BM14)</f>
         <v>0</v>
       </c>
-      <c r="BO14" s="40"/>
-      <c r="BP14" s="40"/>
-      <c r="BQ14" s="42"/>
+      <c r="BO14" s="38"/>
+      <c r="BP14" s="38"/>
+      <c r="BQ14" s="40"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="43" t="s">
+      <c r="A15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="45"/>
-      <c r="AA15" s="45"/>
-      <c r="AB15" s="46"/>
-      <c r="AC15" s="44"/>
-      <c r="AD15" s="45"/>
-      <c r="AE15" s="45"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="44"/>
-      <c r="AH15" s="45"/>
-      <c r="AI15" s="45"/>
-      <c r="AJ15" s="46"/>
-      <c r="AK15" s="44"/>
-      <c r="AL15" s="45"/>
-      <c r="AM15" s="45"/>
-      <c r="AN15" s="46"/>
-      <c r="AO15" s="44"/>
-      <c r="AP15" s="45"/>
-      <c r="AQ15" s="45"/>
-      <c r="AR15" s="46"/>
-      <c r="AS15" s="44"/>
-      <c r="AT15" s="45"/>
-      <c r="AU15" s="45"/>
-      <c r="AV15" s="46"/>
-      <c r="AW15" s="44"/>
-      <c r="AX15" s="45"/>
-      <c r="AY15" s="45"/>
-      <c r="AZ15" s="45"/>
-      <c r="BA15" s="46"/>
-      <c r="BB15" s="44"/>
-      <c r="BC15" s="45"/>
-      <c r="BD15" s="45"/>
-      <c r="BE15" s="46"/>
-      <c r="BF15" s="44"/>
-      <c r="BG15" s="45"/>
-      <c r="BH15" s="45"/>
-      <c r="BI15" s="46"/>
-      <c r="BJ15" s="44"/>
-      <c r="BK15" s="45"/>
-      <c r="BL15" s="45"/>
-      <c r="BM15" s="46"/>
-      <c r="BN15" s="44">
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="42"/>
+      <c r="W15" s="42"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="41"/>
+      <c r="AD15" s="42"/>
+      <c r="AE15" s="42"/>
+      <c r="AF15" s="43"/>
+      <c r="AG15" s="41"/>
+      <c r="AH15" s="42"/>
+      <c r="AI15" s="42"/>
+      <c r="AJ15" s="43"/>
+      <c r="AK15" s="41"/>
+      <c r="AL15" s="42"/>
+      <c r="AM15" s="42"/>
+      <c r="AN15" s="43"/>
+      <c r="AO15" s="41"/>
+      <c r="AP15" s="42"/>
+      <c r="AQ15" s="42"/>
+      <c r="AR15" s="43"/>
+      <c r="AS15" s="41"/>
+      <c r="AT15" s="42"/>
+      <c r="AU15" s="42"/>
+      <c r="AV15" s="43"/>
+      <c r="AW15" s="41"/>
+      <c r="AX15" s="42"/>
+      <c r="AY15" s="42"/>
+      <c r="AZ15" s="42"/>
+      <c r="BA15" s="43"/>
+      <c r="BB15" s="41"/>
+      <c r="BC15" s="42"/>
+      <c r="BD15" s="42"/>
+      <c r="BE15" s="43"/>
+      <c r="BF15" s="41"/>
+      <c r="BG15" s="42"/>
+      <c r="BH15" s="42"/>
+      <c r="BI15" s="43"/>
+      <c r="BJ15" s="41"/>
+      <c r="BK15" s="42"/>
+      <c r="BL15" s="42"/>
+      <c r="BM15" s="43"/>
+      <c r="BN15" s="41">
         <f t="shared" ref="BN15:BN37" si="0">SUM(I15:BM15)</f>
         <v>0</v>
       </c>
-      <c r="BO15" s="45"/>
-      <c r="BP15" s="45"/>
-      <c r="BQ15" s="47"/>
+      <c r="BO15" s="42"/>
+      <c r="BP15" s="42"/>
+      <c r="BQ15" s="44"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43" t="s">
+      <c r="A16" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="44"/>
-      <c r="V16" s="45"/>
-      <c r="W16" s="45"/>
-      <c r="X16" s="46"/>
-      <c r="Y16" s="44"/>
-      <c r="Z16" s="45"/>
-      <c r="AA16" s="45"/>
-      <c r="AB16" s="46"/>
-      <c r="AC16" s="44"/>
-      <c r="AD16" s="45"/>
-      <c r="AE16" s="45"/>
-      <c r="AF16" s="46"/>
-      <c r="AG16" s="44"/>
-      <c r="AH16" s="45"/>
-      <c r="AI16" s="45"/>
-      <c r="AJ16" s="46"/>
-      <c r="AK16" s="44"/>
-      <c r="AL16" s="45"/>
-      <c r="AM16" s="45"/>
-      <c r="AN16" s="46"/>
-      <c r="AO16" s="44"/>
-      <c r="AP16" s="45"/>
-      <c r="AQ16" s="45"/>
-      <c r="AR16" s="46"/>
-      <c r="AS16" s="44"/>
-      <c r="AT16" s="45"/>
-      <c r="AU16" s="45"/>
-      <c r="AV16" s="46"/>
-      <c r="AW16" s="44"/>
-      <c r="AX16" s="45"/>
-      <c r="AY16" s="45"/>
-      <c r="AZ16" s="45"/>
-      <c r="BA16" s="46"/>
-      <c r="BB16" s="44"/>
-      <c r="BC16" s="45"/>
-      <c r="BD16" s="45"/>
-      <c r="BE16" s="46"/>
-      <c r="BF16" s="44"/>
-      <c r="BG16" s="45"/>
-      <c r="BH16" s="45"/>
-      <c r="BI16" s="46"/>
-      <c r="BJ16" s="44"/>
-      <c r="BK16" s="45"/>
-      <c r="BL16" s="45"/>
-      <c r="BM16" s="46"/>
-      <c r="BN16" s="44">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="42"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="42"/>
+      <c r="AA16" s="42"/>
+      <c r="AB16" s="43"/>
+      <c r="AC16" s="41"/>
+      <c r="AD16" s="42"/>
+      <c r="AE16" s="42"/>
+      <c r="AF16" s="43"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="42"/>
+      <c r="AI16" s="42"/>
+      <c r="AJ16" s="43"/>
+      <c r="AK16" s="41"/>
+      <c r="AL16" s="42"/>
+      <c r="AM16" s="42"/>
+      <c r="AN16" s="43"/>
+      <c r="AO16" s="41"/>
+      <c r="AP16" s="42"/>
+      <c r="AQ16" s="42"/>
+      <c r="AR16" s="43"/>
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="42"/>
+      <c r="AU16" s="42"/>
+      <c r="AV16" s="43"/>
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="42"/>
+      <c r="AY16" s="42"/>
+      <c r="AZ16" s="42"/>
+      <c r="BA16" s="43"/>
+      <c r="BB16" s="41"/>
+      <c r="BC16" s="42"/>
+      <c r="BD16" s="42"/>
+      <c r="BE16" s="43"/>
+      <c r="BF16" s="41"/>
+      <c r="BG16" s="42"/>
+      <c r="BH16" s="42"/>
+      <c r="BI16" s="43"/>
+      <c r="BJ16" s="41"/>
+      <c r="BK16" s="42"/>
+      <c r="BL16" s="42"/>
+      <c r="BM16" s="43"/>
+      <c r="BN16" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO16" s="45"/>
-      <c r="BP16" s="45"/>
-      <c r="BQ16" s="47"/>
+      <c r="BO16" s="42"/>
+      <c r="BP16" s="42"/>
+      <c r="BQ16" s="44"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="44"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="44"/>
-      <c r="V17" s="45"/>
-      <c r="W17" s="45"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="44"/>
-      <c r="Z17" s="45"/>
-      <c r="AA17" s="45"/>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="44"/>
-      <c r="AD17" s="45"/>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="44"/>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="45"/>
-      <c r="AJ17" s="46"/>
-      <c r="AK17" s="44"/>
-      <c r="AL17" s="45"/>
-      <c r="AM17" s="45"/>
-      <c r="AN17" s="46"/>
-      <c r="AO17" s="44"/>
-      <c r="AP17" s="45"/>
-      <c r="AQ17" s="45"/>
-      <c r="AR17" s="46"/>
-      <c r="AS17" s="44"/>
-      <c r="AT17" s="45"/>
-      <c r="AU17" s="45"/>
-      <c r="AV17" s="46"/>
-      <c r="AW17" s="44"/>
-      <c r="AX17" s="45"/>
-      <c r="AY17" s="45"/>
-      <c r="AZ17" s="45"/>
-      <c r="BA17" s="46"/>
-      <c r="BB17" s="44"/>
-      <c r="BC17" s="45"/>
-      <c r="BD17" s="45"/>
-      <c r="BE17" s="46"/>
-      <c r="BF17" s="44"/>
-      <c r="BG17" s="45"/>
-      <c r="BH17" s="45"/>
-      <c r="BI17" s="46"/>
-      <c r="BJ17" s="44"/>
-      <c r="BK17" s="45"/>
-      <c r="BL17" s="45"/>
-      <c r="BM17" s="46"/>
-      <c r="BN17" s="44">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="43"/>
+      <c r="Y17" s="41"/>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="43"/>
+      <c r="AC17" s="41"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="43"/>
+      <c r="AG17" s="41"/>
+      <c r="AH17" s="42"/>
+      <c r="AI17" s="42"/>
+      <c r="AJ17" s="43"/>
+      <c r="AK17" s="41"/>
+      <c r="AL17" s="42"/>
+      <c r="AM17" s="42"/>
+      <c r="AN17" s="43"/>
+      <c r="AO17" s="41"/>
+      <c r="AP17" s="42"/>
+      <c r="AQ17" s="42"/>
+      <c r="AR17" s="43"/>
+      <c r="AS17" s="41"/>
+      <c r="AT17" s="42"/>
+      <c r="AU17" s="42"/>
+      <c r="AV17" s="43"/>
+      <c r="AW17" s="41"/>
+      <c r="AX17" s="42"/>
+      <c r="AY17" s="42"/>
+      <c r="AZ17" s="42"/>
+      <c r="BA17" s="43"/>
+      <c r="BB17" s="41"/>
+      <c r="BC17" s="42"/>
+      <c r="BD17" s="42"/>
+      <c r="BE17" s="43"/>
+      <c r="BF17" s="41"/>
+      <c r="BG17" s="42"/>
+      <c r="BH17" s="42"/>
+      <c r="BI17" s="43"/>
+      <c r="BJ17" s="41"/>
+      <c r="BK17" s="42"/>
+      <c r="BL17" s="42"/>
+      <c r="BM17" s="43"/>
+      <c r="BN17" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO17" s="45"/>
-      <c r="BP17" s="45"/>
-      <c r="BQ17" s="47"/>
+      <c r="BO17" s="42"/>
+      <c r="BP17" s="42"/>
+      <c r="BQ17" s="44"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="45"/>
-      <c r="W18" s="45"/>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="44"/>
-      <c r="Z18" s="45"/>
-      <c r="AA18" s="45"/>
-      <c r="AB18" s="46"/>
-      <c r="AC18" s="44"/>
-      <c r="AD18" s="45"/>
-      <c r="AE18" s="45"/>
-      <c r="AF18" s="46"/>
-      <c r="AG18" s="44"/>
-      <c r="AH18" s="45"/>
-      <c r="AI18" s="45"/>
-      <c r="AJ18" s="46"/>
-      <c r="AK18" s="44"/>
-      <c r="AL18" s="45"/>
-      <c r="AM18" s="45"/>
-      <c r="AN18" s="46"/>
-      <c r="AO18" s="44"/>
-      <c r="AP18" s="45"/>
-      <c r="AQ18" s="45"/>
-      <c r="AR18" s="46"/>
-      <c r="AS18" s="44"/>
-      <c r="AT18" s="45"/>
-      <c r="AU18" s="45"/>
-      <c r="AV18" s="46"/>
-      <c r="AW18" s="44"/>
-      <c r="AX18" s="45"/>
-      <c r="AY18" s="45"/>
-      <c r="AZ18" s="45"/>
-      <c r="BA18" s="46"/>
-      <c r="BB18" s="44"/>
-      <c r="BC18" s="45"/>
-      <c r="BD18" s="45"/>
-      <c r="BE18" s="46"/>
-      <c r="BF18" s="44"/>
-      <c r="BG18" s="45"/>
-      <c r="BH18" s="45"/>
-      <c r="BI18" s="46"/>
-      <c r="BJ18" s="44"/>
-      <c r="BK18" s="45"/>
-      <c r="BL18" s="45"/>
-      <c r="BM18" s="46"/>
-      <c r="BN18" s="44">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="43"/>
+      <c r="AC18" s="41"/>
+      <c r="AD18" s="42"/>
+      <c r="AE18" s="42"/>
+      <c r="AF18" s="43"/>
+      <c r="AG18" s="41"/>
+      <c r="AH18" s="42"/>
+      <c r="AI18" s="42"/>
+      <c r="AJ18" s="43"/>
+      <c r="AK18" s="41"/>
+      <c r="AL18" s="42"/>
+      <c r="AM18" s="42"/>
+      <c r="AN18" s="43"/>
+      <c r="AO18" s="41"/>
+      <c r="AP18" s="42"/>
+      <c r="AQ18" s="42"/>
+      <c r="AR18" s="43"/>
+      <c r="AS18" s="41"/>
+      <c r="AT18" s="42"/>
+      <c r="AU18" s="42"/>
+      <c r="AV18" s="43"/>
+      <c r="AW18" s="41"/>
+      <c r="AX18" s="42"/>
+      <c r="AY18" s="42"/>
+      <c r="AZ18" s="42"/>
+      <c r="BA18" s="43"/>
+      <c r="BB18" s="41"/>
+      <c r="BC18" s="42"/>
+      <c r="BD18" s="42"/>
+      <c r="BE18" s="43"/>
+      <c r="BF18" s="41"/>
+      <c r="BG18" s="42"/>
+      <c r="BH18" s="42"/>
+      <c r="BI18" s="43"/>
+      <c r="BJ18" s="41"/>
+      <c r="BK18" s="42"/>
+      <c r="BL18" s="42"/>
+      <c r="BM18" s="43"/>
+      <c r="BN18" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO18" s="45"/>
-      <c r="BP18" s="45"/>
-      <c r="BQ18" s="47"/>
+      <c r="BO18" s="42"/>
+      <c r="BP18" s="42"/>
+      <c r="BQ18" s="44"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="45"/>
-      <c r="W19" s="45"/>
-      <c r="X19" s="46"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="45"/>
-      <c r="AA19" s="45"/>
-      <c r="AB19" s="46"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="45"/>
-      <c r="AE19" s="45"/>
-      <c r="AF19" s="46"/>
-      <c r="AG19" s="44"/>
-      <c r="AH19" s="45"/>
-      <c r="AI19" s="45"/>
-      <c r="AJ19" s="46"/>
-      <c r="AK19" s="44"/>
-      <c r="AL19" s="45"/>
-      <c r="AM19" s="45"/>
-      <c r="AN19" s="46"/>
-      <c r="AO19" s="44"/>
-      <c r="AP19" s="45"/>
-      <c r="AQ19" s="45"/>
-      <c r="AR19" s="46"/>
-      <c r="AS19" s="44"/>
-      <c r="AT19" s="45"/>
-      <c r="AU19" s="45"/>
-      <c r="AV19" s="46"/>
-      <c r="AW19" s="44"/>
-      <c r="AX19" s="45"/>
-      <c r="AY19" s="45"/>
-      <c r="AZ19" s="45"/>
-      <c r="BA19" s="46"/>
-      <c r="BB19" s="44"/>
-      <c r="BC19" s="45"/>
-      <c r="BD19" s="45"/>
-      <c r="BE19" s="46"/>
-      <c r="BF19" s="44"/>
-      <c r="BG19" s="45"/>
-      <c r="BH19" s="45"/>
-      <c r="BI19" s="46"/>
-      <c r="BJ19" s="44"/>
-      <c r="BK19" s="45"/>
-      <c r="BL19" s="45"/>
-      <c r="BM19" s="46"/>
-      <c r="BN19" s="44">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="42"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="41"/>
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="41"/>
+      <c r="AD19" s="42"/>
+      <c r="AE19" s="42"/>
+      <c r="AF19" s="43"/>
+      <c r="AG19" s="41"/>
+      <c r="AH19" s="42"/>
+      <c r="AI19" s="42"/>
+      <c r="AJ19" s="43"/>
+      <c r="AK19" s="41"/>
+      <c r="AL19" s="42"/>
+      <c r="AM19" s="42"/>
+      <c r="AN19" s="43"/>
+      <c r="AO19" s="41"/>
+      <c r="AP19" s="42"/>
+      <c r="AQ19" s="42"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="41"/>
+      <c r="AT19" s="42"/>
+      <c r="AU19" s="42"/>
+      <c r="AV19" s="43"/>
+      <c r="AW19" s="41"/>
+      <c r="AX19" s="42"/>
+      <c r="AY19" s="42"/>
+      <c r="AZ19" s="42"/>
+      <c r="BA19" s="43"/>
+      <c r="BB19" s="41"/>
+      <c r="BC19" s="42"/>
+      <c r="BD19" s="42"/>
+      <c r="BE19" s="43"/>
+      <c r="BF19" s="41"/>
+      <c r="BG19" s="42"/>
+      <c r="BH19" s="42"/>
+      <c r="BI19" s="43"/>
+      <c r="BJ19" s="41"/>
+      <c r="BK19" s="42"/>
+      <c r="BL19" s="42"/>
+      <c r="BM19" s="43"/>
+      <c r="BN19" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO19" s="45"/>
-      <c r="BP19" s="45"/>
-      <c r="BQ19" s="47"/>
+      <c r="BO19" s="42"/>
+      <c r="BP19" s="42"/>
+      <c r="BQ19" s="44"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="44"/>
-      <c r="V20" s="45"/>
-      <c r="W20" s="45"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="44"/>
-      <c r="Z20" s="45"/>
-      <c r="AA20" s="45"/>
-      <c r="AB20" s="46"/>
-      <c r="AC20" s="44"/>
-      <c r="AD20" s="45"/>
-      <c r="AE20" s="45"/>
-      <c r="AF20" s="46"/>
-      <c r="AG20" s="44"/>
-      <c r="AH20" s="45"/>
-      <c r="AI20" s="45"/>
-      <c r="AJ20" s="46"/>
-      <c r="AK20" s="44"/>
-      <c r="AL20" s="45"/>
-      <c r="AM20" s="45"/>
-      <c r="AN20" s="46"/>
-      <c r="AO20" s="44"/>
-      <c r="AP20" s="45"/>
-      <c r="AQ20" s="45"/>
-      <c r="AR20" s="46"/>
-      <c r="AS20" s="44"/>
-      <c r="AT20" s="45"/>
-      <c r="AU20" s="45"/>
-      <c r="AV20" s="46"/>
-      <c r="AW20" s="44"/>
-      <c r="AX20" s="45"/>
-      <c r="AY20" s="45"/>
-      <c r="AZ20" s="45"/>
-      <c r="BA20" s="46"/>
-      <c r="BB20" s="44"/>
-      <c r="BC20" s="45"/>
-      <c r="BD20" s="45"/>
-      <c r="BE20" s="46"/>
-      <c r="BF20" s="44"/>
-      <c r="BG20" s="45"/>
-      <c r="BH20" s="45"/>
-      <c r="BI20" s="46"/>
-      <c r="BJ20" s="44"/>
-      <c r="BK20" s="45"/>
-      <c r="BL20" s="45"/>
-      <c r="BM20" s="46"/>
-      <c r="BN20" s="44">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="42"/>
+      <c r="AE20" s="42"/>
+      <c r="AF20" s="43"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="42"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="43"/>
+      <c r="AK20" s="41"/>
+      <c r="AL20" s="42"/>
+      <c r="AM20" s="42"/>
+      <c r="AN20" s="43"/>
+      <c r="AO20" s="41"/>
+      <c r="AP20" s="42"/>
+      <c r="AQ20" s="42"/>
+      <c r="AR20" s="43"/>
+      <c r="AS20" s="41"/>
+      <c r="AT20" s="42"/>
+      <c r="AU20" s="42"/>
+      <c r="AV20" s="43"/>
+      <c r="AW20" s="41"/>
+      <c r="AX20" s="42"/>
+      <c r="AY20" s="42"/>
+      <c r="AZ20" s="42"/>
+      <c r="BA20" s="43"/>
+      <c r="BB20" s="41"/>
+      <c r="BC20" s="42"/>
+      <c r="BD20" s="42"/>
+      <c r="BE20" s="43"/>
+      <c r="BF20" s="41"/>
+      <c r="BG20" s="42"/>
+      <c r="BH20" s="42"/>
+      <c r="BI20" s="43"/>
+      <c r="BJ20" s="41"/>
+      <c r="BK20" s="42"/>
+      <c r="BL20" s="42"/>
+      <c r="BM20" s="43"/>
+      <c r="BN20" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO20" s="45"/>
-      <c r="BP20" s="45"/>
-      <c r="BQ20" s="47"/>
+      <c r="BO20" s="42"/>
+      <c r="BP20" s="42"/>
+      <c r="BQ20" s="44"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="44"/>
-      <c r="V21" s="45"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="44"/>
-      <c r="Z21" s="45"/>
-      <c r="AA21" s="45"/>
-      <c r="AB21" s="46"/>
-      <c r="AC21" s="44"/>
-      <c r="AD21" s="45"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="44"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="45"/>
-      <c r="AJ21" s="46"/>
-      <c r="AK21" s="44"/>
-      <c r="AL21" s="45"/>
-      <c r="AM21" s="45"/>
-      <c r="AN21" s="46"/>
-      <c r="AO21" s="44"/>
-      <c r="AP21" s="45"/>
-      <c r="AQ21" s="45"/>
-      <c r="AR21" s="46"/>
-      <c r="AS21" s="44"/>
-      <c r="AT21" s="45"/>
-      <c r="AU21" s="45"/>
-      <c r="AV21" s="46"/>
-      <c r="AW21" s="44"/>
-      <c r="AX21" s="45"/>
-      <c r="AY21" s="45"/>
-      <c r="AZ21" s="45"/>
-      <c r="BA21" s="46"/>
-      <c r="BB21" s="44"/>
-      <c r="BC21" s="45"/>
-      <c r="BD21" s="45"/>
-      <c r="BE21" s="46"/>
-      <c r="BF21" s="44"/>
-      <c r="BG21" s="45"/>
-      <c r="BH21" s="45"/>
-      <c r="BI21" s="46"/>
-      <c r="BJ21" s="44"/>
-      <c r="BK21" s="45"/>
-      <c r="BL21" s="45"/>
-      <c r="BM21" s="46"/>
-      <c r="BN21" s="44">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="43"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="41"/>
+      <c r="AD21" s="42"/>
+      <c r="AE21" s="42"/>
+      <c r="AF21" s="43"/>
+      <c r="AG21" s="41"/>
+      <c r="AH21" s="42"/>
+      <c r="AI21" s="42"/>
+      <c r="AJ21" s="43"/>
+      <c r="AK21" s="41"/>
+      <c r="AL21" s="42"/>
+      <c r="AM21" s="42"/>
+      <c r="AN21" s="43"/>
+      <c r="AO21" s="41"/>
+      <c r="AP21" s="42"/>
+      <c r="AQ21" s="42"/>
+      <c r="AR21" s="43"/>
+      <c r="AS21" s="41"/>
+      <c r="AT21" s="42"/>
+      <c r="AU21" s="42"/>
+      <c r="AV21" s="43"/>
+      <c r="AW21" s="41"/>
+      <c r="AX21" s="42"/>
+      <c r="AY21" s="42"/>
+      <c r="AZ21" s="42"/>
+      <c r="BA21" s="43"/>
+      <c r="BB21" s="41"/>
+      <c r="BC21" s="42"/>
+      <c r="BD21" s="42"/>
+      <c r="BE21" s="43"/>
+      <c r="BF21" s="41"/>
+      <c r="BG21" s="42"/>
+      <c r="BH21" s="42"/>
+      <c r="BI21" s="43"/>
+      <c r="BJ21" s="41"/>
+      <c r="BK21" s="42"/>
+      <c r="BL21" s="42"/>
+      <c r="BM21" s="43"/>
+      <c r="BN21" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO21" s="45"/>
-      <c r="BP21" s="45"/>
-      <c r="BQ21" s="47"/>
+      <c r="BO21" s="42"/>
+      <c r="BP21" s="42"/>
+      <c r="BQ21" s="44"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="52"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="52"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="51"/>
-      <c r="V22" s="52"/>
-      <c r="W22" s="52"/>
-      <c r="X22" s="53"/>
-      <c r="Y22" s="51"/>
-      <c r="Z22" s="52"/>
-      <c r="AA22" s="52"/>
-      <c r="AB22" s="53"/>
-      <c r="AC22" s="51"/>
-      <c r="AD22" s="52"/>
-      <c r="AE22" s="52"/>
-      <c r="AF22" s="53"/>
-      <c r="AG22" s="51"/>
-      <c r="AH22" s="52"/>
-      <c r="AI22" s="52"/>
-      <c r="AJ22" s="53"/>
-      <c r="AK22" s="51"/>
-      <c r="AL22" s="52"/>
-      <c r="AM22" s="52"/>
-      <c r="AN22" s="53"/>
-      <c r="AO22" s="51"/>
-      <c r="AP22" s="52"/>
-      <c r="AQ22" s="52"/>
-      <c r="AR22" s="53"/>
-      <c r="AS22" s="51"/>
-      <c r="AT22" s="52"/>
-      <c r="AU22" s="52"/>
-      <c r="AV22" s="53"/>
-      <c r="AW22" s="51"/>
-      <c r="AX22" s="52"/>
-      <c r="AY22" s="52"/>
-      <c r="AZ22" s="52"/>
-      <c r="BA22" s="53"/>
-      <c r="BB22" s="51"/>
-      <c r="BC22" s="52"/>
-      <c r="BD22" s="52"/>
-      <c r="BE22" s="53"/>
-      <c r="BF22" s="51"/>
-      <c r="BG22" s="52"/>
-      <c r="BH22" s="52"/>
-      <c r="BI22" s="53"/>
-      <c r="BJ22" s="51"/>
-      <c r="BK22" s="52"/>
-      <c r="BL22" s="52"/>
-      <c r="BM22" s="53"/>
-      <c r="BN22" s="51">
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="46"/>
+      <c r="V22" s="47"/>
+      <c r="W22" s="47"/>
+      <c r="X22" s="48"/>
+      <c r="Y22" s="46"/>
+      <c r="Z22" s="47"/>
+      <c r="AA22" s="47"/>
+      <c r="AB22" s="48"/>
+      <c r="AC22" s="46"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="48"/>
+      <c r="AG22" s="46"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="48"/>
+      <c r="AK22" s="46"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="47"/>
+      <c r="AN22" s="48"/>
+      <c r="AO22" s="46"/>
+      <c r="AP22" s="47"/>
+      <c r="AQ22" s="47"/>
+      <c r="AR22" s="48"/>
+      <c r="AS22" s="46"/>
+      <c r="AT22" s="47"/>
+      <c r="AU22" s="47"/>
+      <c r="AV22" s="48"/>
+      <c r="AW22" s="46"/>
+      <c r="AX22" s="47"/>
+      <c r="AY22" s="47"/>
+      <c r="AZ22" s="47"/>
+      <c r="BA22" s="48"/>
+      <c r="BB22" s="46"/>
+      <c r="BC22" s="47"/>
+      <c r="BD22" s="47"/>
+      <c r="BE22" s="48"/>
+      <c r="BF22" s="46"/>
+      <c r="BG22" s="47"/>
+      <c r="BH22" s="47"/>
+      <c r="BI22" s="48"/>
+      <c r="BJ22" s="46"/>
+      <c r="BK22" s="47"/>
+      <c r="BL22" s="47"/>
+      <c r="BM22" s="48"/>
+      <c r="BN22" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO22" s="52"/>
-      <c r="BP22" s="52"/>
-      <c r="BQ22" s="54"/>
+      <c r="BO22" s="47"/>
+      <c r="BP22" s="47"/>
+      <c r="BQ22" s="49"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A23" s="55"/>
-      <c r="B23" s="56" t="s">
+      <c r="A23" s="50"/>
+      <c r="B23" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="58">
-        <f>SUM(I14:I21)</f>
-      </c>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="58">
-        <f t="shared" ref="M23" si="1">SUM(M14:M21)</f>
-      </c>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="58">
-        <f t="shared" ref="Q23" si="2">SUM(Q14:Q21)</f>
-      </c>
-      <c r="R23" s="59"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="59"/>
-      <c r="U23" s="58">
-        <f t="shared" ref="U23" si="3">SUM(U14:U21)</f>
-      </c>
-      <c r="V23" s="59"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="59"/>
-      <c r="Y23" s="58">
-        <f t="shared" ref="Y23" si="4">SUM(Y14:Y21)</f>
-      </c>
-      <c r="Z23" s="59"/>
-      <c r="AA23" s="59"/>
-      <c r="AB23" s="59"/>
-      <c r="AC23" s="58">
-        <f t="shared" ref="AC23" si="5">SUM(AC14:AC21)</f>
-      </c>
-      <c r="AD23" s="59"/>
-      <c r="AE23" s="59"/>
-      <c r="AF23" s="59"/>
-      <c r="AG23" s="58">
-        <f t="shared" ref="AG23" si="6">SUM(AG14:AG21)</f>
-      </c>
-      <c r="AH23" s="59"/>
-      <c r="AI23" s="59"/>
-      <c r="AJ23" s="59"/>
-      <c r="AK23" s="58">
-        <f t="shared" ref="AK23" si="7">SUM(AK14:AK21)</f>
-      </c>
-      <c r="AL23" s="59"/>
-      <c r="AM23" s="59"/>
-      <c r="AN23" s="59"/>
-      <c r="AO23" s="58">
-        <f t="shared" ref="AO23" si="8">SUM(AO14:AO21)</f>
-      </c>
-      <c r="AP23" s="59"/>
-      <c r="AQ23" s="59"/>
-      <c r="AR23" s="59"/>
-      <c r="AS23" s="58">
-        <f t="shared" ref="AS23" si="9">SUM(AS14:AS21)</f>
-      </c>
-      <c r="AT23" s="59"/>
-      <c r="AU23" s="59"/>
-      <c r="AV23" s="59"/>
-      <c r="AW23" s="58">
-        <f t="shared" ref="AW23" si="10">SUM(AW14:AW21)</f>
-      </c>
-      <c r="AX23" s="59"/>
-      <c r="AY23" s="59"/>
-      <c r="AZ23" s="59"/>
-      <c r="BA23" s="59"/>
-      <c r="BB23" s="58">
-        <f t="shared" ref="BB23" si="11">SUM(BB14:BB21)</f>
-      </c>
-      <c r="BC23" s="59"/>
-      <c r="BD23" s="59"/>
-      <c r="BE23" s="59"/>
-      <c r="BF23" s="58">
-        <f t="shared" ref="BF23" si="12">SUM(BF14:BF21)</f>
-      </c>
-      <c r="BG23" s="59"/>
-      <c r="BH23" s="59"/>
-      <c r="BI23" s="59"/>
-      <c r="BJ23" s="58">
-        <f t="shared" ref="BJ23" si="13">SUM(BJ14:BJ21)</f>
-      </c>
-      <c r="BK23" s="59"/>
-      <c r="BL23" s="59"/>
-      <c r="BM23" s="59"/>
-      <c r="BN23" s="58">
-        <f>SUM(BN14:BN21)</f>
-      </c>
-      <c r="BO23" s="59"/>
-      <c r="BP23" s="59"/>
-      <c r="BQ23" s="59"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="53">
+        <f>SUM(I14:I22)</f>
+      </c>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="53">
+        <f>SUM(M14:M22)</f>
+      </c>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="53">
+        <f>SUM(Q14:Q22)</f>
+      </c>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="53">
+        <f>SUM(U14:U22)</f>
+      </c>
+      <c r="V23" s="54"/>
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="53">
+        <f>SUM(Y14:Y22)</f>
+      </c>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="53">
+        <f>SUM(AC14:AC22)</f>
+      </c>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="54"/>
+      <c r="AG23" s="53">
+        <f>SUM(AG14:AG22)</f>
+      </c>
+      <c r="AH23" s="54"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="54"/>
+      <c r="AK23" s="53">
+        <f>SUM(AK14:AK22)</f>
+      </c>
+      <c r="AL23" s="54"/>
+      <c r="AM23" s="54"/>
+      <c r="AN23" s="54"/>
+      <c r="AO23" s="53">
+        <f>SUM(AO14:AO22)</f>
+      </c>
+      <c r="AP23" s="54"/>
+      <c r="AQ23" s="54"/>
+      <c r="AR23" s="54"/>
+      <c r="AS23" s="53">
+        <f>SUM(AS14:AS22)</f>
+      </c>
+      <c r="AT23" s="54"/>
+      <c r="AU23" s="54"/>
+      <c r="AV23" s="54"/>
+      <c r="AW23" s="53">
+        <f>SUM(AW14:AW22)</f>
+      </c>
+      <c r="AX23" s="54"/>
+      <c r="AY23" s="54"/>
+      <c r="AZ23" s="54"/>
+      <c r="BA23" s="54"/>
+      <c r="BB23" s="53">
+        <f>SUM(BB14:BB22)</f>
+      </c>
+      <c r="BC23" s="54"/>
+      <c r="BD23" s="54"/>
+      <c r="BE23" s="54"/>
+      <c r="BF23" s="53">
+        <f>SUM(BF14:BF22)</f>
+      </c>
+      <c r="BG23" s="54"/>
+      <c r="BH23" s="54"/>
+      <c r="BI23" s="54"/>
+      <c r="BJ23" s="53">
+        <f>SUM(BJ14:BJ22)</f>
+      </c>
+      <c r="BK23" s="54"/>
+      <c r="BL23" s="54"/>
+      <c r="BM23" s="54"/>
+      <c r="BN23" s="53">
+        <f>SUM(BN14:BN22)</f>
+      </c>
+      <c r="BO23" s="54"/>
+      <c r="BP23" s="54"/>
+      <c r="BQ23" s="54"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56" t="s">
+      <c r="A24" s="50"/>
+      <c r="B24" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="58">
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="53">
         <f>I22</f>
         <v>0</v>
       </c>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="58">
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="53">
         <f>M22</f>
         <v>0</v>
       </c>
-      <c r="N24" s="59"/>
-      <c r="O24" s="59"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="58">
-        <v>0</v>
-      </c>
-      <c r="R24" s="59"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="59"/>
-      <c r="U24" s="58">
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="53">
+        <v>0</v>
+      </c>
+      <c r="R24" s="54"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="53">
         <f>U22</f>
         <v>0</v>
       </c>
-      <c r="V24" s="59"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="59"/>
-      <c r="Y24" s="58">
+      <c r="V24" s="54"/>
+      <c r="W24" s="54"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="53">
         <f>Y22</f>
         <v>0</v>
       </c>
-      <c r="Z24" s="59"/>
-      <c r="AA24" s="59"/>
-      <c r="AB24" s="59"/>
-      <c r="AC24" s="58">
+      <c r="Z24" s="54"/>
+      <c r="AA24" s="54"/>
+      <c r="AB24" s="54"/>
+      <c r="AC24" s="53">
         <f>AC22</f>
         <v>0</v>
       </c>
-      <c r="AD24" s="59"/>
-      <c r="AE24" s="59"/>
-      <c r="AF24" s="59"/>
-      <c r="AG24" s="58">
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="54"/>
+      <c r="AF24" s="54"/>
+      <c r="AG24" s="53">
         <f>AG22</f>
         <v>0</v>
       </c>
-      <c r="AH24" s="59"/>
-      <c r="AI24" s="59"/>
-      <c r="AJ24" s="59"/>
-      <c r="AK24" s="58">
+      <c r="AH24" s="54"/>
+      <c r="AI24" s="54"/>
+      <c r="AJ24" s="54"/>
+      <c r="AK24" s="53">
         <f>AK22</f>
         <v>0</v>
       </c>
-      <c r="AL24" s="59"/>
-      <c r="AM24" s="59"/>
-      <c r="AN24" s="59"/>
-      <c r="AO24" s="58">
+      <c r="AL24" s="54"/>
+      <c r="AM24" s="54"/>
+      <c r="AN24" s="54"/>
+      <c r="AO24" s="53">
         <f>AO22</f>
         <v>0</v>
       </c>
-      <c r="AP24" s="59"/>
-      <c r="AQ24" s="59"/>
-      <c r="AR24" s="59"/>
-      <c r="AS24" s="58">
+      <c r="AP24" s="54"/>
+      <c r="AQ24" s="54"/>
+      <c r="AR24" s="54"/>
+      <c r="AS24" s="53">
         <f>AS22</f>
         <v>0</v>
       </c>
-      <c r="AT24" s="59"/>
-      <c r="AU24" s="59"/>
-      <c r="AV24" s="59"/>
-      <c r="AW24" s="58">
+      <c r="AT24" s="54"/>
+      <c r="AU24" s="54"/>
+      <c r="AV24" s="54"/>
+      <c r="AW24" s="53">
         <f>AW22</f>
         <v>0</v>
       </c>
-      <c r="AX24" s="59"/>
-      <c r="AY24" s="59"/>
-      <c r="AZ24" s="59"/>
-      <c r="BA24" s="59"/>
-      <c r="BB24" s="58">
-        <f t="shared" ref="BB24" si="14">BB22</f>
-        <v>0</v>
-      </c>
-      <c r="BC24" s="59"/>
-      <c r="BD24" s="59"/>
-      <c r="BE24" s="59"/>
-      <c r="BF24" s="58">
-        <f t="shared" ref="BF24" si="15">BF22</f>
-        <v>0</v>
-      </c>
-      <c r="BG24" s="59"/>
-      <c r="BH24" s="59"/>
-      <c r="BI24" s="59"/>
-      <c r="BJ24" s="58">
-        <f t="shared" ref="BJ24" si="16">BJ22</f>
-        <v>0</v>
-      </c>
-      <c r="BK24" s="59"/>
-      <c r="BL24" s="59"/>
-      <c r="BM24" s="59"/>
-      <c r="BN24" s="58">
+      <c r="AX24" s="54"/>
+      <c r="AY24" s="54"/>
+      <c r="AZ24" s="54"/>
+      <c r="BA24" s="54"/>
+      <c r="BB24" s="53">
+        <f t="shared" ref="BB24" si="1">BB22</f>
+        <v>0</v>
+      </c>
+      <c r="BC24" s="54"/>
+      <c r="BD24" s="54"/>
+      <c r="BE24" s="54"/>
+      <c r="BF24" s="53">
+        <f t="shared" ref="BF24" si="2">BF22</f>
+        <v>0</v>
+      </c>
+      <c r="BG24" s="54"/>
+      <c r="BH24" s="54"/>
+      <c r="BI24" s="54"/>
+      <c r="BJ24" s="53">
+        <f t="shared" ref="BJ24" si="3">BJ22</f>
+        <v>0</v>
+      </c>
+      <c r="BK24" s="54"/>
+      <c r="BL24" s="54"/>
+      <c r="BM24" s="54"/>
+      <c r="BN24" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO24" s="59"/>
-      <c r="BP24" s="59"/>
-      <c r="BQ24" s="60"/>
+      <c r="BO24" s="54"/>
+      <c r="BP24" s="54"/>
+      <c r="BQ24" s="55"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56" t="s">
+      <c r="A25" s="50"/>
+      <c r="B25" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58">
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="53">
         <f>I23+I24</f>
         <v>0</v>
       </c>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="58">
-        <f t="shared" ref="M25" si="17">M23+M24</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="58">
-        <f t="shared" ref="Q25" si="18">Q23+Q24</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="59"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="61"/>
-      <c r="U25" s="58">
-        <f t="shared" ref="U25" si="19">U23+U24</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="59"/>
-      <c r="W25" s="59"/>
-      <c r="X25" s="61"/>
-      <c r="Y25" s="58">
-        <f t="shared" ref="Y25" si="20">Y23+Y24</f>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="59"/>
-      <c r="AA25" s="59"/>
-      <c r="AB25" s="61"/>
-      <c r="AC25" s="58">
-        <f t="shared" ref="AC25" si="21">AC23+AC24</f>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="59"/>
-      <c r="AE25" s="59"/>
-      <c r="AF25" s="61"/>
-      <c r="AG25" s="58">
-        <f t="shared" ref="AG25" si="22">AG23+AG24</f>
-        <v>0</v>
-      </c>
-      <c r="AH25" s="59"/>
-      <c r="AI25" s="59"/>
-      <c r="AJ25" s="61"/>
-      <c r="AK25" s="58">
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="53">
+        <f t="shared" ref="M25" si="4">M23+M24</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="53">
+        <f t="shared" ref="Q25" si="5">Q23+Q24</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="54"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="56"/>
+      <c r="U25" s="53">
+        <f t="shared" ref="U25" si="6">U23+U24</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="54"/>
+      <c r="W25" s="54"/>
+      <c r="X25" s="56"/>
+      <c r="Y25" s="53">
+        <f t="shared" ref="Y25" si="7">Y23+Y24</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="54"/>
+      <c r="AA25" s="54"/>
+      <c r="AB25" s="56"/>
+      <c r="AC25" s="53">
+        <f t="shared" ref="AC25" si="8">AC23+AC24</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="54"/>
+      <c r="AF25" s="56"/>
+      <c r="AG25" s="53">
+        <f t="shared" ref="AG25" si="9">AG23+AG24</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="54"/>
+      <c r="AI25" s="54"/>
+      <c r="AJ25" s="56"/>
+      <c r="AK25" s="53">
         <f>AK23+AK24</f>
         <v>0</v>
       </c>
-      <c r="AL25" s="59"/>
-      <c r="AM25" s="59"/>
-      <c r="AN25" s="61"/>
-      <c r="AO25" s="58">
+      <c r="AL25" s="54"/>
+      <c r="AM25" s="54"/>
+      <c r="AN25" s="56"/>
+      <c r="AO25" s="53">
         <f>AO23+AO24</f>
         <v>0</v>
       </c>
-      <c r="AP25" s="59"/>
-      <c r="AQ25" s="59"/>
-      <c r="AR25" s="61"/>
-      <c r="AS25" s="58">
+      <c r="AP25" s="54"/>
+      <c r="AQ25" s="54"/>
+      <c r="AR25" s="56"/>
+      <c r="AS25" s="53">
         <f>AS23+AS24</f>
         <v>0</v>
       </c>
-      <c r="AT25" s="59"/>
-      <c r="AU25" s="59"/>
-      <c r="AV25" s="61"/>
-      <c r="AW25" s="58">
+      <c r="AT25" s="54"/>
+      <c r="AU25" s="54"/>
+      <c r="AV25" s="56"/>
+      <c r="AW25" s="53">
         <f>SUM(AW23:BA24)</f>
         <v>0</v>
       </c>
-      <c r="AX25" s="59"/>
-      <c r="AY25" s="59"/>
-      <c r="AZ25" s="59"/>
-      <c r="BA25" s="61"/>
-      <c r="BB25" s="58">
+      <c r="AX25" s="54"/>
+      <c r="AY25" s="54"/>
+      <c r="AZ25" s="54"/>
+      <c r="BA25" s="56"/>
+      <c r="BB25" s="53">
         <f>BB23+BB24</f>
         <v>0</v>
       </c>
-      <c r="BC25" s="59"/>
-      <c r="BD25" s="59"/>
-      <c r="BE25" s="61"/>
-      <c r="BF25" s="58">
+      <c r="BC25" s="54"/>
+      <c r="BD25" s="54"/>
+      <c r="BE25" s="56"/>
+      <c r="BF25" s="53">
         <f>BF23+BF24</f>
         <v>0</v>
       </c>
-      <c r="BG25" s="59"/>
-      <c r="BH25" s="59"/>
-      <c r="BI25" s="61"/>
-      <c r="BJ25" s="58">
+      <c r="BG25" s="54"/>
+      <c r="BH25" s="54"/>
+      <c r="BI25" s="56"/>
+      <c r="BJ25" s="53">
         <f>BJ23+BJ24</f>
         <v>0</v>
       </c>
-      <c r="BK25" s="59"/>
-      <c r="BL25" s="59"/>
-      <c r="BM25" s="61"/>
-      <c r="BN25" s="58">
+      <c r="BK25" s="54"/>
+      <c r="BL25" s="54"/>
+      <c r="BM25" s="56"/>
+      <c r="BN25" s="53">
         <f>BN23+BN24</f>
         <v>0</v>
       </c>
-      <c r="BO25" s="59"/>
-      <c r="BP25" s="59"/>
-      <c r="BQ25" s="61"/>
+      <c r="BO25" s="54"/>
+      <c r="BP25" s="54"/>
+      <c r="BQ25" s="56"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A26" s="62"/>
-      <c r="B26" s="63" t="s">
+      <c r="A26" s="57"/>
+      <c r="B26" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="65"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="67"/>
-      <c r="Y26" s="65"/>
-      <c r="Z26" s="66"/>
-      <c r="AA26" s="66"/>
-      <c r="AB26" s="67"/>
-      <c r="AC26" s="65"/>
-      <c r="AD26" s="66"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="67"/>
-      <c r="AG26" s="65"/>
-      <c r="AH26" s="66"/>
-      <c r="AI26" s="66"/>
-      <c r="AJ26" s="67"/>
-      <c r="AK26" s="65"/>
-      <c r="AL26" s="66"/>
-      <c r="AM26" s="66"/>
-      <c r="AN26" s="67"/>
-      <c r="AO26" s="65"/>
-      <c r="AP26" s="66"/>
-      <c r="AQ26" s="66"/>
-      <c r="AR26" s="67"/>
-      <c r="AS26" s="65"/>
-      <c r="AT26" s="66"/>
-      <c r="AU26" s="66"/>
-      <c r="AV26" s="67"/>
-      <c r="AW26" s="65"/>
-      <c r="AX26" s="66"/>
-      <c r="AY26" s="66"/>
-      <c r="AZ26" s="66"/>
-      <c r="BA26" s="67"/>
-      <c r="BB26" s="65"/>
-      <c r="BC26" s="66"/>
-      <c r="BD26" s="66"/>
-      <c r="BE26" s="67"/>
-      <c r="BF26" s="65"/>
-      <c r="BG26" s="66"/>
-      <c r="BH26" s="66"/>
-      <c r="BI26" s="67"/>
-      <c r="BJ26" s="65"/>
-      <c r="BK26" s="66"/>
-      <c r="BL26" s="66"/>
-      <c r="BM26" s="67"/>
-      <c r="BN26" s="65">
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="61"/>
+      <c r="X26" s="62"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="61"/>
+      <c r="AB26" s="62"/>
+      <c r="AC26" s="60"/>
+      <c r="AD26" s="61"/>
+      <c r="AE26" s="61"/>
+      <c r="AF26" s="62"/>
+      <c r="AG26" s="60"/>
+      <c r="AH26" s="61"/>
+      <c r="AI26" s="61"/>
+      <c r="AJ26" s="62"/>
+      <c r="AK26" s="60"/>
+      <c r="AL26" s="61"/>
+      <c r="AM26" s="61"/>
+      <c r="AN26" s="62"/>
+      <c r="AO26" s="60"/>
+      <c r="AP26" s="61"/>
+      <c r="AQ26" s="61"/>
+      <c r="AR26" s="62"/>
+      <c r="AS26" s="60"/>
+      <c r="AT26" s="61"/>
+      <c r="AU26" s="61"/>
+      <c r="AV26" s="62"/>
+      <c r="AW26" s="60"/>
+      <c r="AX26" s="61"/>
+      <c r="AY26" s="61"/>
+      <c r="AZ26" s="61"/>
+      <c r="BA26" s="62"/>
+      <c r="BB26" s="60"/>
+      <c r="BC26" s="61"/>
+      <c r="BD26" s="61"/>
+      <c r="BE26" s="62"/>
+      <c r="BF26" s="60"/>
+      <c r="BG26" s="61"/>
+      <c r="BH26" s="61"/>
+      <c r="BI26" s="62"/>
+      <c r="BJ26" s="60"/>
+      <c r="BK26" s="61"/>
+      <c r="BL26" s="61"/>
+      <c r="BM26" s="62"/>
+      <c r="BN26" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO26" s="66"/>
-      <c r="BP26" s="66"/>
-      <c r="BQ26" s="68"/>
+      <c r="BO26" s="61"/>
+      <c r="BP26" s="61"/>
+      <c r="BQ26" s="63"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
@@ -3005,70 +2976,70 @@
       <c r="F27" s="25"/>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="44"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="45"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="44"/>
-      <c r="Z27" s="45"/>
-      <c r="AA27" s="45"/>
-      <c r="AB27" s="46"/>
-      <c r="AC27" s="44"/>
-      <c r="AD27" s="45"/>
-      <c r="AE27" s="45"/>
-      <c r="AF27" s="46"/>
-      <c r="AG27" s="44"/>
-      <c r="AH27" s="45"/>
-      <c r="AI27" s="45"/>
-      <c r="AJ27" s="46"/>
-      <c r="AK27" s="44"/>
-      <c r="AL27" s="45"/>
-      <c r="AM27" s="45"/>
-      <c r="AN27" s="46"/>
-      <c r="AO27" s="44"/>
-      <c r="AP27" s="45"/>
-      <c r="AQ27" s="45"/>
-      <c r="AR27" s="46"/>
-      <c r="AS27" s="44"/>
-      <c r="AT27" s="45"/>
-      <c r="AU27" s="45"/>
-      <c r="AV27" s="46"/>
-      <c r="AW27" s="44"/>
-      <c r="AX27" s="45"/>
-      <c r="AY27" s="45"/>
-      <c r="AZ27" s="45"/>
-      <c r="BA27" s="46"/>
-      <c r="BB27" s="44"/>
-      <c r="BC27" s="45"/>
-      <c r="BD27" s="45"/>
-      <c r="BE27" s="46"/>
-      <c r="BF27" s="44"/>
-      <c r="BG27" s="45"/>
-      <c r="BH27" s="45"/>
-      <c r="BI27" s="46"/>
-      <c r="BJ27" s="44"/>
-      <c r="BK27" s="45"/>
-      <c r="BL27" s="45"/>
-      <c r="BM27" s="46"/>
-      <c r="BN27" s="44">
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="42"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="42"/>
+      <c r="W27" s="42"/>
+      <c r="X27" s="43"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="42"/>
+      <c r="AA27" s="42"/>
+      <c r="AB27" s="43"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="42"/>
+      <c r="AE27" s="42"/>
+      <c r="AF27" s="43"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="42"/>
+      <c r="AI27" s="42"/>
+      <c r="AJ27" s="43"/>
+      <c r="AK27" s="41"/>
+      <c r="AL27" s="42"/>
+      <c r="AM27" s="42"/>
+      <c r="AN27" s="43"/>
+      <c r="AO27" s="41"/>
+      <c r="AP27" s="42"/>
+      <c r="AQ27" s="42"/>
+      <c r="AR27" s="43"/>
+      <c r="AS27" s="41"/>
+      <c r="AT27" s="42"/>
+      <c r="AU27" s="42"/>
+      <c r="AV27" s="43"/>
+      <c r="AW27" s="41"/>
+      <c r="AX27" s="42"/>
+      <c r="AY27" s="42"/>
+      <c r="AZ27" s="42"/>
+      <c r="BA27" s="43"/>
+      <c r="BB27" s="41"/>
+      <c r="BC27" s="42"/>
+      <c r="BD27" s="42"/>
+      <c r="BE27" s="43"/>
+      <c r="BF27" s="41"/>
+      <c r="BG27" s="42"/>
+      <c r="BH27" s="42"/>
+      <c r="BI27" s="43"/>
+      <c r="BJ27" s="41"/>
+      <c r="BK27" s="42"/>
+      <c r="BL27" s="42"/>
+      <c r="BM27" s="43"/>
+      <c r="BN27" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO27" s="45"/>
-      <c r="BP27" s="45"/>
-      <c r="BQ27" s="47"/>
+      <c r="BO27" s="42"/>
+      <c r="BP27" s="42"/>
+      <c r="BQ27" s="44"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
@@ -3081,456 +3052,456 @@
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
       <c r="H28" s="26"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="X28" s="46"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="45"/>
-      <c r="AA28" s="45"/>
-      <c r="AB28" s="46"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="45"/>
-      <c r="AE28" s="45"/>
-      <c r="AF28" s="46"/>
-      <c r="AG28" s="44"/>
-      <c r="AH28" s="45"/>
-      <c r="AI28" s="45"/>
-      <c r="AJ28" s="46"/>
-      <c r="AK28" s="44"/>
-      <c r="AL28" s="45"/>
-      <c r="AM28" s="45"/>
-      <c r="AN28" s="46"/>
-      <c r="AO28" s="44"/>
-      <c r="AP28" s="45"/>
-      <c r="AQ28" s="45"/>
-      <c r="AR28" s="46"/>
-      <c r="AS28" s="44"/>
-      <c r="AT28" s="45"/>
-      <c r="AU28" s="45"/>
-      <c r="AV28" s="46"/>
-      <c r="AW28" s="44"/>
-      <c r="AX28" s="45"/>
-      <c r="AY28" s="45"/>
-      <c r="AZ28" s="45"/>
-      <c r="BA28" s="46"/>
-      <c r="BB28" s="44"/>
-      <c r="BC28" s="45"/>
-      <c r="BD28" s="45"/>
-      <c r="BE28" s="46"/>
-      <c r="BF28" s="44"/>
-      <c r="BG28" s="45"/>
-      <c r="BH28" s="45"/>
-      <c r="BI28" s="46"/>
-      <c r="BJ28" s="44"/>
-      <c r="BK28" s="45"/>
-      <c r="BL28" s="45"/>
-      <c r="BM28" s="46"/>
-      <c r="BN28" s="44">
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="42"/>
+      <c r="W28" s="42"/>
+      <c r="X28" s="43"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="42"/>
+      <c r="AA28" s="42"/>
+      <c r="AB28" s="43"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="42"/>
+      <c r="AE28" s="42"/>
+      <c r="AF28" s="43"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="43"/>
+      <c r="AK28" s="41"/>
+      <c r="AL28" s="42"/>
+      <c r="AM28" s="42"/>
+      <c r="AN28" s="43"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="42"/>
+      <c r="AQ28" s="42"/>
+      <c r="AR28" s="43"/>
+      <c r="AS28" s="41"/>
+      <c r="AT28" s="42"/>
+      <c r="AU28" s="42"/>
+      <c r="AV28" s="43"/>
+      <c r="AW28" s="41"/>
+      <c r="AX28" s="42"/>
+      <c r="AY28" s="42"/>
+      <c r="AZ28" s="42"/>
+      <c r="BA28" s="43"/>
+      <c r="BB28" s="41"/>
+      <c r="BC28" s="42"/>
+      <c r="BD28" s="42"/>
+      <c r="BE28" s="43"/>
+      <c r="BF28" s="41"/>
+      <c r="BG28" s="42"/>
+      <c r="BH28" s="42"/>
+      <c r="BI28" s="43"/>
+      <c r="BJ28" s="41"/>
+      <c r="BK28" s="42"/>
+      <c r="BL28" s="42"/>
+      <c r="BM28" s="43"/>
+      <c r="BN28" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO28" s="45"/>
-      <c r="BP28" s="45"/>
-      <c r="BQ28" s="47"/>
+      <c r="BO28" s="42"/>
+      <c r="BP28" s="42"/>
+      <c r="BQ28" s="44"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A29" s="69"/>
-      <c r="B29" s="70" t="s">
+      <c r="A29" s="64"/>
+      <c r="B29" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="53"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="53"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="52"/>
-      <c r="W29" s="52"/>
-      <c r="X29" s="53"/>
-      <c r="Y29" s="51"/>
-      <c r="Z29" s="52"/>
-      <c r="AA29" s="52"/>
-      <c r="AB29" s="53"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="52"/>
-      <c r="AE29" s="52"/>
-      <c r="AF29" s="53"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="52"/>
-      <c r="AI29" s="52"/>
-      <c r="AJ29" s="53"/>
-      <c r="AK29" s="51"/>
-      <c r="AL29" s="52"/>
-      <c r="AM29" s="52"/>
-      <c r="AN29" s="53"/>
-      <c r="AO29" s="51"/>
-      <c r="AP29" s="52"/>
-      <c r="AQ29" s="52"/>
-      <c r="AR29" s="53"/>
-      <c r="AS29" s="51"/>
-      <c r="AT29" s="52"/>
-      <c r="AU29" s="52"/>
-      <c r="AV29" s="53"/>
-      <c r="AW29" s="51"/>
-      <c r="AX29" s="52"/>
-      <c r="AY29" s="52"/>
-      <c r="AZ29" s="52"/>
-      <c r="BA29" s="53"/>
-      <c r="BB29" s="51"/>
-      <c r="BC29" s="52"/>
-      <c r="BD29" s="52"/>
-      <c r="BE29" s="53"/>
-      <c r="BF29" s="51"/>
-      <c r="BG29" s="52"/>
-      <c r="BH29" s="52"/>
-      <c r="BI29" s="53"/>
-      <c r="BJ29" s="51"/>
-      <c r="BK29" s="52"/>
-      <c r="BL29" s="52"/>
-      <c r="BM29" s="53"/>
-      <c r="BN29" s="51">
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="47"/>
+      <c r="W29" s="47"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="47"/>
+      <c r="AB29" s="48"/>
+      <c r="AC29" s="46"/>
+      <c r="AD29" s="47"/>
+      <c r="AE29" s="47"/>
+      <c r="AF29" s="48"/>
+      <c r="AG29" s="46"/>
+      <c r="AH29" s="47"/>
+      <c r="AI29" s="47"/>
+      <c r="AJ29" s="48"/>
+      <c r="AK29" s="46"/>
+      <c r="AL29" s="47"/>
+      <c r="AM29" s="47"/>
+      <c r="AN29" s="48"/>
+      <c r="AO29" s="46"/>
+      <c r="AP29" s="47"/>
+      <c r="AQ29" s="47"/>
+      <c r="AR29" s="48"/>
+      <c r="AS29" s="46"/>
+      <c r="AT29" s="47"/>
+      <c r="AU29" s="47"/>
+      <c r="AV29" s="48"/>
+      <c r="AW29" s="46"/>
+      <c r="AX29" s="47"/>
+      <c r="AY29" s="47"/>
+      <c r="AZ29" s="47"/>
+      <c r="BA29" s="48"/>
+      <c r="BB29" s="46"/>
+      <c r="BC29" s="47"/>
+      <c r="BD29" s="47"/>
+      <c r="BE29" s="48"/>
+      <c r="BF29" s="46"/>
+      <c r="BG29" s="47"/>
+      <c r="BH29" s="47"/>
+      <c r="BI29" s="48"/>
+      <c r="BJ29" s="46"/>
+      <c r="BK29" s="47"/>
+      <c r="BL29" s="47"/>
+      <c r="BM29" s="48"/>
+      <c r="BN29" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO29" s="52"/>
-      <c r="BP29" s="52"/>
-      <c r="BQ29" s="54"/>
+      <c r="BO29" s="47"/>
+      <c r="BP29" s="47"/>
+      <c r="BQ29" s="49"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
-      <c r="B30" s="56" t="s">
+      <c r="A30" s="50"/>
+      <c r="B30" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="58">
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53">
         <f>SUM(I26:I29)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="58">
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="53">
         <f>SUM(M26:M29)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="59"/>
-      <c r="O30" s="59"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="58">
-        <f t="shared" ref="Q30" si="23">SUM(Q26:Q29)</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="59"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="58">
-        <f t="shared" ref="U30" si="24">SUM(U26:U29)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="59"/>
-      <c r="W30" s="59"/>
-      <c r="X30" s="61"/>
-      <c r="Y30" s="58">
-        <f t="shared" ref="Y30" si="25">SUM(Y26:Y29)</f>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="59"/>
-      <c r="AA30" s="59"/>
-      <c r="AB30" s="61"/>
-      <c r="AC30" s="58">
-        <f t="shared" ref="AC30" si="26">SUM(AC26:AC29)</f>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="59"/>
-      <c r="AE30" s="59"/>
-      <c r="AF30" s="61"/>
-      <c r="AG30" s="58">
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="53">
+        <f t="shared" ref="Q30" si="10">SUM(Q26:Q29)</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="54"/>
+      <c r="S30" s="54"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="53">
+        <f t="shared" ref="U30" si="11">SUM(U26:U29)</f>
+        <v>0</v>
+      </c>
+      <c r="V30" s="54"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="56"/>
+      <c r="Y30" s="53">
+        <f t="shared" ref="Y30" si="12">SUM(Y26:Y29)</f>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="54"/>
+      <c r="AB30" s="56"/>
+      <c r="AC30" s="53">
+        <f t="shared" ref="AC30" si="13">SUM(AC26:AC29)</f>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="54"/>
+      <c r="AE30" s="54"/>
+      <c r="AF30" s="56"/>
+      <c r="AG30" s="53">
         <f>SUM(AG26:AG29)</f>
         <v>0</v>
       </c>
-      <c r="AH30" s="59"/>
-      <c r="AI30" s="59"/>
-      <c r="AJ30" s="61"/>
-      <c r="AK30" s="58">
+      <c r="AH30" s="54"/>
+      <c r="AI30" s="54"/>
+      <c r="AJ30" s="56"/>
+      <c r="AK30" s="53">
         <f>SUM(AK26:AK29)</f>
         <v>0</v>
       </c>
-      <c r="AL30" s="59"/>
-      <c r="AM30" s="59"/>
-      <c r="AN30" s="61"/>
-      <c r="AO30" s="58">
+      <c r="AL30" s="54"/>
+      <c r="AM30" s="54"/>
+      <c r="AN30" s="56"/>
+      <c r="AO30" s="53">
         <f>SUM(AO26:AO29)</f>
         <v>0</v>
       </c>
-      <c r="AP30" s="59"/>
-      <c r="AQ30" s="59"/>
-      <c r="AR30" s="61"/>
-      <c r="AS30" s="58">
+      <c r="AP30" s="54"/>
+      <c r="AQ30" s="54"/>
+      <c r="AR30" s="56"/>
+      <c r="AS30" s="53">
         <f>SUM(AS26:AS29)</f>
         <v>0</v>
       </c>
-      <c r="AT30" s="59"/>
-      <c r="AU30" s="59"/>
-      <c r="AV30" s="61"/>
-      <c r="AW30" s="58">
-        <v>0</v>
-      </c>
-      <c r="AX30" s="59"/>
-      <c r="AY30" s="59"/>
-      <c r="AZ30" s="59"/>
-      <c r="BA30" s="61"/>
-      <c r="BB30" s="58">
+      <c r="AT30" s="54"/>
+      <c r="AU30" s="54"/>
+      <c r="AV30" s="56"/>
+      <c r="AW30" s="53">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="54"/>
+      <c r="AY30" s="54"/>
+      <c r="AZ30" s="54"/>
+      <c r="BA30" s="56"/>
+      <c r="BB30" s="53">
         <f>SUM(BB26:BB29)</f>
         <v>0</v>
       </c>
-      <c r="BC30" s="59"/>
-      <c r="BD30" s="59"/>
-      <c r="BE30" s="61"/>
-      <c r="BF30" s="58">
+      <c r="BC30" s="54"/>
+      <c r="BD30" s="54"/>
+      <c r="BE30" s="56"/>
+      <c r="BF30" s="53">
         <f>SUM(BF26:BF29)</f>
         <v>0</v>
       </c>
-      <c r="BG30" s="59"/>
-      <c r="BH30" s="59"/>
-      <c r="BI30" s="61"/>
-      <c r="BJ30" s="58">
+      <c r="BG30" s="54"/>
+      <c r="BH30" s="54"/>
+      <c r="BI30" s="56"/>
+      <c r="BJ30" s="53">
         <f>SUM(BJ26:BJ29)</f>
         <v>0</v>
       </c>
-      <c r="BK30" s="59"/>
-      <c r="BL30" s="59"/>
-      <c r="BM30" s="61"/>
-      <c r="BN30" s="58">
+      <c r="BK30" s="54"/>
+      <c r="BL30" s="54"/>
+      <c r="BM30" s="56"/>
+      <c r="BN30" s="53">
         <f>SUM(BN26:BN29)</f>
         <v>0</v>
       </c>
-      <c r="BO30" s="59"/>
-      <c r="BP30" s="59"/>
-      <c r="BQ30" s="61"/>
+      <c r="BO30" s="54"/>
+      <c r="BP30" s="54"/>
+      <c r="BQ30" s="56"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="56" t="s">
+      <c r="A31" s="50"/>
+      <c r="B31" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="58">
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="53">
         <f>I23-I30</f>
         <v>0</v>
       </c>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="58">
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="53">
         <f>M23-M30</f>
         <v>0</v>
       </c>
-      <c r="N31" s="59"/>
-      <c r="O31" s="59"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="58">
+      <c r="N31" s="54"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="53">
         <f>Q23-Q30</f>
         <v>0</v>
       </c>
-      <c r="R31" s="59"/>
-      <c r="S31" s="59"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="58">
+      <c r="R31" s="54"/>
+      <c r="S31" s="54"/>
+      <c r="T31" s="56"/>
+      <c r="U31" s="53">
         <f>U23-U30</f>
         <v>0</v>
       </c>
-      <c r="V31" s="59"/>
-      <c r="W31" s="59"/>
-      <c r="X31" s="61"/>
-      <c r="Y31" s="58">
+      <c r="V31" s="54"/>
+      <c r="W31" s="54"/>
+      <c r="X31" s="56"/>
+      <c r="Y31" s="53">
         <f>Y23-Y30</f>
         <v>0</v>
       </c>
-      <c r="Z31" s="59"/>
-      <c r="AA31" s="59"/>
-      <c r="AB31" s="61"/>
-      <c r="AC31" s="58">
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="54"/>
+      <c r="AB31" s="56"/>
+      <c r="AC31" s="53">
         <f>AC23-AC30</f>
         <v>0</v>
       </c>
-      <c r="AD31" s="59"/>
-      <c r="AE31" s="59"/>
-      <c r="AF31" s="61"/>
-      <c r="AG31" s="58">
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="56"/>
+      <c r="AG31" s="53">
         <f>AG23-AG30</f>
         <v>0</v>
       </c>
-      <c r="AH31" s="59"/>
-      <c r="AI31" s="59"/>
-      <c r="AJ31" s="61"/>
-      <c r="AK31" s="58">
+      <c r="AH31" s="54"/>
+      <c r="AI31" s="54"/>
+      <c r="AJ31" s="56"/>
+      <c r="AK31" s="53">
         <f>AK23-AK30</f>
         <v>0</v>
       </c>
-      <c r="AL31" s="59"/>
-      <c r="AM31" s="59"/>
-      <c r="AN31" s="61"/>
-      <c r="AO31" s="58">
+      <c r="AL31" s="54"/>
+      <c r="AM31" s="54"/>
+      <c r="AN31" s="56"/>
+      <c r="AO31" s="53">
         <f>AO23-AO30</f>
         <v>0</v>
       </c>
-      <c r="AP31" s="59"/>
-      <c r="AQ31" s="59"/>
-      <c r="AR31" s="61"/>
-      <c r="AS31" s="58">
+      <c r="AP31" s="54"/>
+      <c r="AQ31" s="54"/>
+      <c r="AR31" s="56"/>
+      <c r="AS31" s="53">
         <f>AS23-AS30</f>
         <v>0</v>
       </c>
-      <c r="AT31" s="59"/>
-      <c r="AU31" s="59"/>
-      <c r="AV31" s="61"/>
-      <c r="AW31" s="58">
-        <v>0</v>
-      </c>
-      <c r="AX31" s="59"/>
-      <c r="AY31" s="59"/>
-      <c r="AZ31" s="59"/>
-      <c r="BA31" s="61"/>
-      <c r="BB31" s="58">
+      <c r="AT31" s="54"/>
+      <c r="AU31" s="54"/>
+      <c r="AV31" s="56"/>
+      <c r="AW31" s="53">
+        <v>0</v>
+      </c>
+      <c r="AX31" s="54"/>
+      <c r="AY31" s="54"/>
+      <c r="AZ31" s="54"/>
+      <c r="BA31" s="56"/>
+      <c r="BB31" s="53">
         <f>BB23-BB30</f>
         <v>0</v>
       </c>
-      <c r="BC31" s="59"/>
-      <c r="BD31" s="59"/>
-      <c r="BE31" s="61"/>
-      <c r="BF31" s="58">
+      <c r="BC31" s="54"/>
+      <c r="BD31" s="54"/>
+      <c r="BE31" s="56"/>
+      <c r="BF31" s="53">
         <f>BF23-BF30</f>
         <v>0</v>
       </c>
-      <c r="BG31" s="59"/>
-      <c r="BH31" s="59"/>
-      <c r="BI31" s="61"/>
-      <c r="BJ31" s="58">
+      <c r="BG31" s="54"/>
+      <c r="BH31" s="54"/>
+      <c r="BI31" s="56"/>
+      <c r="BJ31" s="53">
         <f>BJ23-BJ30</f>
         <v>0</v>
       </c>
-      <c r="BK31" s="59"/>
-      <c r="BL31" s="59"/>
-      <c r="BM31" s="61"/>
-      <c r="BN31" s="58">
+      <c r="BK31" s="54"/>
+      <c r="BL31" s="54"/>
+      <c r="BM31" s="56"/>
+      <c r="BN31" s="53">
         <f>BN23-BN30</f>
         <v>0</v>
       </c>
-      <c r="BO31" s="59"/>
-      <c r="BP31" s="59"/>
-      <c r="BQ31" s="61"/>
+      <c r="BO31" s="54"/>
+      <c r="BP31" s="54"/>
+      <c r="BQ31" s="56"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A32" s="62"/>
-      <c r="B32" s="63" t="s">
+      <c r="A32" s="57"/>
+      <c r="B32" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="67"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="67"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="66"/>
-      <c r="X32" s="67"/>
-      <c r="Y32" s="65"/>
-      <c r="Z32" s="66"/>
-      <c r="AA32" s="66"/>
-      <c r="AB32" s="67"/>
-      <c r="AC32" s="65"/>
-      <c r="AD32" s="66"/>
-      <c r="AE32" s="66"/>
-      <c r="AF32" s="67"/>
-      <c r="AG32" s="65"/>
-      <c r="AH32" s="66"/>
-      <c r="AI32" s="66"/>
-      <c r="AJ32" s="67"/>
-      <c r="AK32" s="65"/>
-      <c r="AL32" s="66"/>
-      <c r="AM32" s="66"/>
-      <c r="AN32" s="67"/>
-      <c r="AO32" s="65"/>
-      <c r="AP32" s="66"/>
-      <c r="AQ32" s="66"/>
-      <c r="AR32" s="67"/>
-      <c r="AS32" s="65"/>
-      <c r="AT32" s="66"/>
-      <c r="AU32" s="66"/>
-      <c r="AV32" s="67"/>
-      <c r="AW32" s="65"/>
-      <c r="AX32" s="66"/>
-      <c r="AY32" s="66"/>
-      <c r="AZ32" s="66"/>
-      <c r="BA32" s="67"/>
-      <c r="BB32" s="65"/>
-      <c r="BC32" s="66"/>
-      <c r="BD32" s="66"/>
-      <c r="BE32" s="67"/>
-      <c r="BF32" s="65"/>
-      <c r="BG32" s="66"/>
-      <c r="BH32" s="66"/>
-      <c r="BI32" s="67"/>
-      <c r="BJ32" s="65"/>
-      <c r="BK32" s="66"/>
-      <c r="BL32" s="66"/>
-      <c r="BM32" s="67"/>
-      <c r="BN32" s="65">
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="62"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="62"/>
+      <c r="Y32" s="60"/>
+      <c r="Z32" s="61"/>
+      <c r="AA32" s="61"/>
+      <c r="AB32" s="62"/>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="61"/>
+      <c r="AE32" s="61"/>
+      <c r="AF32" s="62"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="61"/>
+      <c r="AI32" s="61"/>
+      <c r="AJ32" s="62"/>
+      <c r="AK32" s="60"/>
+      <c r="AL32" s="61"/>
+      <c r="AM32" s="61"/>
+      <c r="AN32" s="62"/>
+      <c r="AO32" s="60"/>
+      <c r="AP32" s="61"/>
+      <c r="AQ32" s="61"/>
+      <c r="AR32" s="62"/>
+      <c r="AS32" s="60"/>
+      <c r="AT32" s="61"/>
+      <c r="AU32" s="61"/>
+      <c r="AV32" s="62"/>
+      <c r="AW32" s="60"/>
+      <c r="AX32" s="61"/>
+      <c r="AY32" s="61"/>
+      <c r="AZ32" s="61"/>
+      <c r="BA32" s="62"/>
+      <c r="BB32" s="60"/>
+      <c r="BC32" s="61"/>
+      <c r="BD32" s="61"/>
+      <c r="BE32" s="62"/>
+      <c r="BF32" s="60"/>
+      <c r="BG32" s="61"/>
+      <c r="BH32" s="61"/>
+      <c r="BI32" s="62"/>
+      <c r="BJ32" s="60"/>
+      <c r="BK32" s="61"/>
+      <c r="BL32" s="61"/>
+      <c r="BM32" s="62"/>
+      <c r="BN32" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO32" s="66"/>
-      <c r="BP32" s="66"/>
-      <c r="BQ32" s="68"/>
+      <c r="BO32" s="61"/>
+      <c r="BP32" s="61"/>
+      <c r="BQ32" s="63"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
@@ -3543,70 +3514,70 @@
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
       <c r="H33" s="26"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="46"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="44"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="46"/>
-      <c r="Y33" s="44"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="46"/>
-      <c r="AC33" s="44"/>
-      <c r="AD33" s="45"/>
-      <c r="AE33" s="45"/>
-      <c r="AF33" s="46"/>
-      <c r="AG33" s="44"/>
-      <c r="AH33" s="45"/>
-      <c r="AI33" s="45"/>
-      <c r="AJ33" s="46"/>
-      <c r="AK33" s="44"/>
-      <c r="AL33" s="45"/>
-      <c r="AM33" s="45"/>
-      <c r="AN33" s="46"/>
-      <c r="AO33" s="44"/>
-      <c r="AP33" s="45"/>
-      <c r="AQ33" s="45"/>
-      <c r="AR33" s="46"/>
-      <c r="AS33" s="44"/>
-      <c r="AT33" s="45"/>
-      <c r="AU33" s="45"/>
-      <c r="AV33" s="46"/>
-      <c r="AW33" s="44"/>
-      <c r="AX33" s="45"/>
-      <c r="AY33" s="45"/>
-      <c r="AZ33" s="45"/>
-      <c r="BA33" s="46"/>
-      <c r="BB33" s="44"/>
-      <c r="BC33" s="45"/>
-      <c r="BD33" s="45"/>
-      <c r="BE33" s="46"/>
-      <c r="BF33" s="44"/>
-      <c r="BG33" s="45"/>
-      <c r="BH33" s="45"/>
-      <c r="BI33" s="46"/>
-      <c r="BJ33" s="44"/>
-      <c r="BK33" s="45"/>
-      <c r="BL33" s="45"/>
-      <c r="BM33" s="46"/>
-      <c r="BN33" s="44">
+      <c r="I33" s="41"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="42"/>
+      <c r="W33" s="42"/>
+      <c r="X33" s="43"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="42"/>
+      <c r="AA33" s="42"/>
+      <c r="AB33" s="43"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="42"/>
+      <c r="AE33" s="42"/>
+      <c r="AF33" s="43"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="42"/>
+      <c r="AI33" s="42"/>
+      <c r="AJ33" s="43"/>
+      <c r="AK33" s="41"/>
+      <c r="AL33" s="42"/>
+      <c r="AM33" s="42"/>
+      <c r="AN33" s="43"/>
+      <c r="AO33" s="41"/>
+      <c r="AP33" s="42"/>
+      <c r="AQ33" s="42"/>
+      <c r="AR33" s="43"/>
+      <c r="AS33" s="41"/>
+      <c r="AT33" s="42"/>
+      <c r="AU33" s="42"/>
+      <c r="AV33" s="43"/>
+      <c r="AW33" s="41"/>
+      <c r="AX33" s="42"/>
+      <c r="AY33" s="42"/>
+      <c r="AZ33" s="42"/>
+      <c r="BA33" s="43"/>
+      <c r="BB33" s="41"/>
+      <c r="BC33" s="42"/>
+      <c r="BD33" s="42"/>
+      <c r="BE33" s="43"/>
+      <c r="BF33" s="41"/>
+      <c r="BG33" s="42"/>
+      <c r="BH33" s="42"/>
+      <c r="BI33" s="43"/>
+      <c r="BJ33" s="41"/>
+      <c r="BK33" s="42"/>
+      <c r="BL33" s="42"/>
+      <c r="BM33" s="43"/>
+      <c r="BN33" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO33" s="45"/>
-      <c r="BP33" s="45"/>
-      <c r="BQ33" s="47"/>
+      <c r="BO33" s="42"/>
+      <c r="BP33" s="42"/>
+      <c r="BQ33" s="44"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
@@ -3617,383 +3588,383 @@
       <c r="F34" s="25"/>
       <c r="G34" s="25"/>
       <c r="H34" s="26"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="46"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="44"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="46"/>
-      <c r="Y34" s="44"/>
-      <c r="Z34" s="45"/>
-      <c r="AA34" s="45"/>
-      <c r="AB34" s="46"/>
-      <c r="AC34" s="44"/>
-      <c r="AD34" s="45"/>
-      <c r="AE34" s="45"/>
-      <c r="AF34" s="46"/>
-      <c r="AG34" s="44"/>
-      <c r="AH34" s="45"/>
-      <c r="AI34" s="45"/>
-      <c r="AJ34" s="46"/>
-      <c r="AK34" s="44"/>
-      <c r="AL34" s="45"/>
-      <c r="AM34" s="45"/>
-      <c r="AN34" s="46"/>
-      <c r="AO34" s="44"/>
-      <c r="AP34" s="45"/>
-      <c r="AQ34" s="45"/>
-      <c r="AR34" s="46"/>
-      <c r="AS34" s="44"/>
-      <c r="AT34" s="45"/>
-      <c r="AU34" s="45"/>
-      <c r="AV34" s="46"/>
-      <c r="AW34" s="44"/>
-      <c r="AX34" s="45"/>
-      <c r="AY34" s="45"/>
-      <c r="AZ34" s="45"/>
-      <c r="BA34" s="46"/>
-      <c r="BB34" s="44"/>
-      <c r="BC34" s="45"/>
-      <c r="BD34" s="45"/>
-      <c r="BE34" s="46"/>
-      <c r="BF34" s="44"/>
-      <c r="BG34" s="45"/>
-      <c r="BH34" s="45"/>
-      <c r="BI34" s="46"/>
-      <c r="BJ34" s="44"/>
-      <c r="BK34" s="45"/>
-      <c r="BL34" s="45"/>
-      <c r="BM34" s="46"/>
-      <c r="BN34" s="44">
+      <c r="I34" s="41"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="42"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="42"/>
+      <c r="X34" s="43"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="42"/>
+      <c r="AA34" s="42"/>
+      <c r="AB34" s="43"/>
+      <c r="AC34" s="41"/>
+      <c r="AD34" s="42"/>
+      <c r="AE34" s="42"/>
+      <c r="AF34" s="43"/>
+      <c r="AG34" s="41"/>
+      <c r="AH34" s="42"/>
+      <c r="AI34" s="42"/>
+      <c r="AJ34" s="43"/>
+      <c r="AK34" s="41"/>
+      <c r="AL34" s="42"/>
+      <c r="AM34" s="42"/>
+      <c r="AN34" s="43"/>
+      <c r="AO34" s="41"/>
+      <c r="AP34" s="42"/>
+      <c r="AQ34" s="42"/>
+      <c r="AR34" s="43"/>
+      <c r="AS34" s="41"/>
+      <c r="AT34" s="42"/>
+      <c r="AU34" s="42"/>
+      <c r="AV34" s="43"/>
+      <c r="AW34" s="41"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="43"/>
+      <c r="BB34" s="41"/>
+      <c r="BC34" s="42"/>
+      <c r="BD34" s="42"/>
+      <c r="BE34" s="43"/>
+      <c r="BF34" s="41"/>
+      <c r="BG34" s="42"/>
+      <c r="BH34" s="42"/>
+      <c r="BI34" s="43"/>
+      <c r="BJ34" s="41"/>
+      <c r="BK34" s="42"/>
+      <c r="BL34" s="42"/>
+      <c r="BM34" s="43"/>
+      <c r="BN34" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO34" s="45"/>
-      <c r="BP34" s="45"/>
-      <c r="BQ34" s="47"/>
+      <c r="BO34" s="42"/>
+      <c r="BP34" s="42"/>
+      <c r="BQ34" s="44"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A35" s="69"/>
-      <c r="B35" s="71" t="s">
+      <c r="A35" s="64"/>
+      <c r="B35" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="51"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="73"/>
-      <c r="R35" s="74"/>
-      <c r="S35" s="74"/>
-      <c r="T35" s="75"/>
-      <c r="U35" s="51"/>
-      <c r="V35" s="52"/>
-      <c r="W35" s="52"/>
-      <c r="X35" s="53"/>
-      <c r="Y35" s="51"/>
-      <c r="Z35" s="52"/>
-      <c r="AA35" s="52"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="51"/>
-      <c r="AD35" s="52"/>
-      <c r="AE35" s="52"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="51"/>
-      <c r="AH35" s="52"/>
-      <c r="AI35" s="52"/>
-      <c r="AJ35" s="53"/>
-      <c r="AK35" s="51"/>
-      <c r="AL35" s="52"/>
-      <c r="AM35" s="52"/>
-      <c r="AN35" s="53"/>
-      <c r="AO35" s="51"/>
-      <c r="AP35" s="52"/>
-      <c r="AQ35" s="52"/>
-      <c r="AR35" s="53"/>
-      <c r="AS35" s="51"/>
-      <c r="AT35" s="52"/>
-      <c r="AU35" s="52"/>
-      <c r="AV35" s="53"/>
-      <c r="AW35" s="51"/>
-      <c r="AX35" s="52"/>
-      <c r="AY35" s="52"/>
-      <c r="AZ35" s="52"/>
-      <c r="BA35" s="53"/>
-      <c r="BB35" s="51"/>
-      <c r="BC35" s="52"/>
-      <c r="BD35" s="52"/>
-      <c r="BE35" s="53"/>
-      <c r="BF35" s="51"/>
-      <c r="BG35" s="52"/>
-      <c r="BH35" s="52"/>
-      <c r="BI35" s="53"/>
-      <c r="BJ35" s="51"/>
-      <c r="BK35" s="52"/>
-      <c r="BL35" s="52"/>
-      <c r="BM35" s="53"/>
-      <c r="BN35" s="51">
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="68"/>
+      <c r="R35" s="69"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="47"/>
+      <c r="W35" s="47"/>
+      <c r="X35" s="48"/>
+      <c r="Y35" s="46"/>
+      <c r="Z35" s="47"/>
+      <c r="AA35" s="47"/>
+      <c r="AB35" s="48"/>
+      <c r="AC35" s="46"/>
+      <c r="AD35" s="47"/>
+      <c r="AE35" s="47"/>
+      <c r="AF35" s="48"/>
+      <c r="AG35" s="46"/>
+      <c r="AH35" s="47"/>
+      <c r="AI35" s="47"/>
+      <c r="AJ35" s="48"/>
+      <c r="AK35" s="46"/>
+      <c r="AL35" s="47"/>
+      <c r="AM35" s="47"/>
+      <c r="AN35" s="48"/>
+      <c r="AO35" s="46"/>
+      <c r="AP35" s="47"/>
+      <c r="AQ35" s="47"/>
+      <c r="AR35" s="48"/>
+      <c r="AS35" s="46"/>
+      <c r="AT35" s="47"/>
+      <c r="AU35" s="47"/>
+      <c r="AV35" s="48"/>
+      <c r="AW35" s="46"/>
+      <c r="AX35" s="47"/>
+      <c r="AY35" s="47"/>
+      <c r="AZ35" s="47"/>
+      <c r="BA35" s="48"/>
+      <c r="BB35" s="46"/>
+      <c r="BC35" s="47"/>
+      <c r="BD35" s="47"/>
+      <c r="BE35" s="48"/>
+      <c r="BF35" s="46"/>
+      <c r="BG35" s="47"/>
+      <c r="BH35" s="47"/>
+      <c r="BI35" s="48"/>
+      <c r="BJ35" s="46"/>
+      <c r="BK35" s="47"/>
+      <c r="BL35" s="47"/>
+      <c r="BM35" s="48"/>
+      <c r="BN35" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO35" s="52"/>
-      <c r="BP35" s="52"/>
-      <c r="BQ35" s="54"/>
+      <c r="BO35" s="47"/>
+      <c r="BP35" s="47"/>
+      <c r="BQ35" s="49"/>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A36" s="55"/>
-      <c r="B36" s="56" t="s">
+      <c r="A36" s="50"/>
+      <c r="B36" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58">
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="53">
         <f>SUM(I32:L35)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="59"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
-      <c r="M36" s="58">
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="53">
         <f>SUM(M32:P35)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="59"/>
-      <c r="O36" s="59"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="58">
+      <c r="N36" s="54"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="54"/>
+      <c r="Q36" s="53">
         <f>SUM(Q32:T35)</f>
         <v>0</v>
       </c>
-      <c r="R36" s="59"/>
-      <c r="S36" s="59"/>
-      <c r="T36" s="59"/>
-      <c r="U36" s="58">
+      <c r="R36" s="54"/>
+      <c r="S36" s="54"/>
+      <c r="T36" s="54"/>
+      <c r="U36" s="53">
         <f>SUM(U32:X35)</f>
         <v>0</v>
       </c>
-      <c r="V36" s="59"/>
-      <c r="W36" s="59"/>
-      <c r="X36" s="59"/>
-      <c r="Y36" s="58">
+      <c r="V36" s="54"/>
+      <c r="W36" s="54"/>
+      <c r="X36" s="54"/>
+      <c r="Y36" s="53">
         <f>SUM(Y32:AB35)</f>
         <v>0</v>
       </c>
-      <c r="Z36" s="59"/>
-      <c r="AA36" s="59"/>
-      <c r="AB36" s="59"/>
-      <c r="AC36" s="58">
+      <c r="Z36" s="54"/>
+      <c r="AA36" s="54"/>
+      <c r="AB36" s="54"/>
+      <c r="AC36" s="53">
         <f>SUM(AC32:AF35)</f>
         <v>0</v>
       </c>
-      <c r="AD36" s="59"/>
-      <c r="AE36" s="59"/>
-      <c r="AF36" s="59"/>
-      <c r="AG36" s="58">
+      <c r="AD36" s="54"/>
+      <c r="AE36" s="54"/>
+      <c r="AF36" s="54"/>
+      <c r="AG36" s="53">
         <f>SUM(AG32:AJ35)</f>
         <v>0</v>
       </c>
-      <c r="AH36" s="59"/>
-      <c r="AI36" s="59"/>
-      <c r="AJ36" s="59"/>
-      <c r="AK36" s="58">
+      <c r="AH36" s="54"/>
+      <c r="AI36" s="54"/>
+      <c r="AJ36" s="54"/>
+      <c r="AK36" s="53">
         <f>SUM(AK32:AN35)</f>
         <v>0</v>
       </c>
-      <c r="AL36" s="59"/>
-      <c r="AM36" s="59"/>
-      <c r="AN36" s="59"/>
-      <c r="AO36" s="58">
+      <c r="AL36" s="54"/>
+      <c r="AM36" s="54"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="53">
         <f>SUM(AO32:AR35)</f>
         <v>0</v>
       </c>
-      <c r="AP36" s="59"/>
-      <c r="AQ36" s="59"/>
-      <c r="AR36" s="59"/>
-      <c r="AS36" s="58">
+      <c r="AP36" s="54"/>
+      <c r="AQ36" s="54"/>
+      <c r="AR36" s="54"/>
+      <c r="AS36" s="53">
         <f>SUM(AS32:AV35)</f>
         <v>0</v>
       </c>
-      <c r="AT36" s="59"/>
-      <c r="AU36" s="59"/>
-      <c r="AV36" s="59"/>
-      <c r="AW36" s="58">
-        <v>0</v>
-      </c>
-      <c r="AX36" s="59"/>
-      <c r="AY36" s="59"/>
-      <c r="AZ36" s="59"/>
-      <c r="BA36" s="59"/>
-      <c r="BB36" s="58">
+      <c r="AT36" s="54"/>
+      <c r="AU36" s="54"/>
+      <c r="AV36" s="54"/>
+      <c r="AW36" s="53">
+        <v>0</v>
+      </c>
+      <c r="AX36" s="54"/>
+      <c r="AY36" s="54"/>
+      <c r="AZ36" s="54"/>
+      <c r="BA36" s="54"/>
+      <c r="BB36" s="53">
         <f>SUM(BB32:BE35)</f>
         <v>0</v>
       </c>
-      <c r="BC36" s="59"/>
-      <c r="BD36" s="59"/>
-      <c r="BE36" s="59"/>
-      <c r="BF36" s="58">
+      <c r="BC36" s="54"/>
+      <c r="BD36" s="54"/>
+      <c r="BE36" s="54"/>
+      <c r="BF36" s="53">
         <f>SUM(BF32:BI35)</f>
         <v>0</v>
       </c>
-      <c r="BG36" s="59"/>
-      <c r="BH36" s="59"/>
-      <c r="BI36" s="59"/>
-      <c r="BJ36" s="58">
+      <c r="BG36" s="54"/>
+      <c r="BH36" s="54"/>
+      <c r="BI36" s="54"/>
+      <c r="BJ36" s="53">
         <f>SUM(BJ32:BM35)</f>
         <v>0</v>
       </c>
-      <c r="BK36" s="59"/>
-      <c r="BL36" s="59"/>
-      <c r="BM36" s="59"/>
-      <c r="BN36" s="58">
+      <c r="BK36" s="54"/>
+      <c r="BL36" s="54"/>
+      <c r="BM36" s="54"/>
+      <c r="BN36" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO36" s="59"/>
-      <c r="BP36" s="59"/>
-      <c r="BQ36" s="60"/>
+      <c r="BO36" s="54"/>
+      <c r="BP36" s="54"/>
+      <c r="BQ36" s="55"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="A37" s="55"/>
-      <c r="B37" s="56" t="s">
+      <c r="A37" s="50"/>
+      <c r="B37" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58">
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="53">
         <f>I25-I30-I36</f>
         <v>0</v>
       </c>
-      <c r="J37" s="59"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="58">
+      <c r="J37" s="54"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="53">
         <f>M25-M30-M36</f>
         <v>0</v>
       </c>
-      <c r="N37" s="59"/>
-      <c r="O37" s="59"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="58">
+      <c r="N37" s="54"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="53">
         <f>Q25-Q30-Q36</f>
         <v>0</v>
       </c>
-      <c r="R37" s="59"/>
-      <c r="S37" s="59"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="58">
+      <c r="R37" s="54"/>
+      <c r="S37" s="54"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="53">
         <f>U25-U30-U36</f>
         <v>0</v>
       </c>
-      <c r="V37" s="59"/>
-      <c r="W37" s="59"/>
-      <c r="X37" s="61"/>
-      <c r="Y37" s="58">
+      <c r="V37" s="54"/>
+      <c r="W37" s="54"/>
+      <c r="X37" s="56"/>
+      <c r="Y37" s="53">
         <f>Y25-Y30-Y36</f>
         <v>0</v>
       </c>
-      <c r="Z37" s="59"/>
-      <c r="AA37" s="59"/>
-      <c r="AB37" s="61"/>
-      <c r="AC37" s="58">
+      <c r="Z37" s="54"/>
+      <c r="AA37" s="54"/>
+      <c r="AB37" s="56"/>
+      <c r="AC37" s="53">
         <f>AC25-AC30-AC36</f>
         <v>0</v>
       </c>
-      <c r="AD37" s="59"/>
-      <c r="AE37" s="59"/>
-      <c r="AF37" s="61"/>
-      <c r="AG37" s="58">
+      <c r="AD37" s="54"/>
+      <c r="AE37" s="54"/>
+      <c r="AF37" s="56"/>
+      <c r="AG37" s="53">
         <f>AG25-AG30-AG36</f>
         <v>0</v>
       </c>
-      <c r="AH37" s="59"/>
-      <c r="AI37" s="59"/>
-      <c r="AJ37" s="61"/>
-      <c r="AK37" s="58">
+      <c r="AH37" s="54"/>
+      <c r="AI37" s="54"/>
+      <c r="AJ37" s="56"/>
+      <c r="AK37" s="53">
         <f>AK25-AK30-AK36</f>
         <v>0</v>
       </c>
-      <c r="AL37" s="59"/>
-      <c r="AM37" s="59"/>
-      <c r="AN37" s="61"/>
-      <c r="AO37" s="58">
+      <c r="AL37" s="54"/>
+      <c r="AM37" s="54"/>
+      <c r="AN37" s="56"/>
+      <c r="AO37" s="53">
         <f>AO25-AO30-AO36</f>
         <v>0</v>
       </c>
-      <c r="AP37" s="59"/>
-      <c r="AQ37" s="59"/>
-      <c r="AR37" s="61"/>
-      <c r="AS37" s="58">
+      <c r="AP37" s="54"/>
+      <c r="AQ37" s="54"/>
+      <c r="AR37" s="56"/>
+      <c r="AS37" s="53">
         <f>AS25-AS30-AS36</f>
         <v>0</v>
       </c>
-      <c r="AT37" s="59"/>
-      <c r="AU37" s="59"/>
-      <c r="AV37" s="61"/>
-      <c r="AW37" s="58">
-        <v>0</v>
-      </c>
-      <c r="AX37" s="59"/>
-      <c r="AY37" s="59"/>
-      <c r="AZ37" s="59"/>
-      <c r="BA37" s="61"/>
-      <c r="BB37" s="58">
+      <c r="AT37" s="54"/>
+      <c r="AU37" s="54"/>
+      <c r="AV37" s="56"/>
+      <c r="AW37" s="53">
+        <v>0</v>
+      </c>
+      <c r="AX37" s="54"/>
+      <c r="AY37" s="54"/>
+      <c r="AZ37" s="54"/>
+      <c r="BA37" s="56"/>
+      <c r="BB37" s="53">
         <f>BB25-BB30-BB36</f>
         <v>0</v>
       </c>
-      <c r="BC37" s="59"/>
-      <c r="BD37" s="59"/>
-      <c r="BE37" s="61"/>
-      <c r="BF37" s="58">
+      <c r="BC37" s="54"/>
+      <c r="BD37" s="54"/>
+      <c r="BE37" s="56"/>
+      <c r="BF37" s="53">
         <f>BF25-BF30-BF36</f>
         <v>0</v>
       </c>
-      <c r="BG37" s="59"/>
-      <c r="BH37" s="59"/>
-      <c r="BI37" s="61"/>
-      <c r="BJ37" s="58">
+      <c r="BG37" s="54"/>
+      <c r="BH37" s="54"/>
+      <c r="BI37" s="56"/>
+      <c r="BJ37" s="53">
         <f>BJ25-BJ30-BJ36</f>
         <v>0</v>
       </c>
-      <c r="BK37" s="59"/>
-      <c r="BL37" s="59"/>
-      <c r="BM37" s="61"/>
-      <c r="BN37" s="58">
+      <c r="BK37" s="54"/>
+      <c r="BL37" s="54"/>
+      <c r="BM37" s="56"/>
+      <c r="BN37" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO37" s="59"/>
-      <c r="BP37" s="59"/>
-      <c r="BQ37" s="60"/>
+      <c r="BO37" s="54"/>
+      <c r="BP37" s="54"/>
+      <c r="BQ37" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="503">
+  <mergeCells count="507">
     <mergeCell ref="A2:BQ2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="I4:P4"/>
@@ -4117,7 +4088,7 @@
     <mergeCell ref="BF13:BI13"/>
     <mergeCell ref="BJ13:BM13"/>
     <mergeCell ref="BN13:BQ13"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="Q14:T14"/>
@@ -4133,6 +4104,7 @@
     <mergeCell ref="BF14:BI14"/>
     <mergeCell ref="BJ14:BM14"/>
     <mergeCell ref="BN14:BQ14"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="I15:L15"/>
     <mergeCell ref="M15:P15"/>
     <mergeCell ref="Q15:T15"/>
@@ -4148,6 +4120,7 @@
     <mergeCell ref="BF15:BI15"/>
     <mergeCell ref="BJ15:BM15"/>
     <mergeCell ref="BN15:BQ15"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="I16:L16"/>
     <mergeCell ref="M16:P16"/>
     <mergeCell ref="Q16:T16"/>
@@ -4163,6 +4136,7 @@
     <mergeCell ref="BF16:BI16"/>
     <mergeCell ref="BJ16:BM16"/>
     <mergeCell ref="BN16:BQ16"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="I17:L17"/>
     <mergeCell ref="M17:P17"/>
     <mergeCell ref="Q17:T17"/>
@@ -4178,7 +4152,7 @@
     <mergeCell ref="BF17:BI17"/>
     <mergeCell ref="BJ17:BM17"/>
     <mergeCell ref="BN17:BQ17"/>
-    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="I18:L18"/>
     <mergeCell ref="M18:P18"/>
     <mergeCell ref="Q18:T18"/>
@@ -4194,7 +4168,7 @@
     <mergeCell ref="BF18:BI18"/>
     <mergeCell ref="BJ18:BM18"/>
     <mergeCell ref="BN18:BQ18"/>
-    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="I19:L19"/>
     <mergeCell ref="M19:P19"/>
     <mergeCell ref="Q19:T19"/>
@@ -4210,7 +4184,7 @@
     <mergeCell ref="BF19:BI19"/>
     <mergeCell ref="BJ19:BM19"/>
     <mergeCell ref="BN19:BQ19"/>
-    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="I20:L20"/>
     <mergeCell ref="M20:P20"/>
     <mergeCell ref="Q20:T20"/>
@@ -4226,7 +4200,7 @@
     <mergeCell ref="BF20:BI20"/>
     <mergeCell ref="BJ20:BM20"/>
     <mergeCell ref="BN20:BQ20"/>
-    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="Q21:T21"/>
@@ -4242,6 +4216,7 @@
     <mergeCell ref="BF21:BI21"/>
     <mergeCell ref="BJ21:BM21"/>
     <mergeCell ref="BN21:BQ21"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="Q22:T22"/>
